--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
@@ -1210,6 +1210,60 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>dry_bulk</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.942</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.035</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>elevated</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>earnings-driven (tool&gt;cons)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1051,7 +1051,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1061,40 +1061,40 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E12" t="n">
-        <v>5.5</v>
+        <v>13.9</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>1.727</v>
       </c>
       <c r="G12" t="n">
-        <v>19.883</v>
+        <v>4.293</v>
       </c>
       <c r="H12" t="n">
-        <v>2.21</v>
+        <v>5.59</v>
       </c>
       <c r="I12" t="n">
-        <v>148.5</v>
+        <v>148.6</v>
       </c>
       <c r="J12" t="n">
-        <v>18.18</v>
+        <v>7.19</v>
       </c>
       <c r="K12" t="n">
-        <v>1.978</v>
+        <v>1.144</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>mid-cycle</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1115,40 +1115,40 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E13" t="n">
-        <v>14.2</v>
+        <v>5.5</v>
       </c>
       <c r="F13" t="n">
-        <v>1.127</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>2.364</v>
+        <v>19.883</v>
       </c>
       <c r="H13" t="n">
-        <v>6.77</v>
+        <v>2.21</v>
       </c>
       <c r="I13" t="n">
-        <v>109.8</v>
+        <v>148.5</v>
       </c>
       <c r="J13" t="n">
-        <v>7.04</v>
+        <v>18.18</v>
       </c>
       <c r="K13" t="n">
-        <v>1.375</v>
+        <v>1.978</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1169,40 +1169,40 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>29.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="F14" t="n">
-        <v>2.048</v>
+        <v>1.127</v>
       </c>
       <c r="G14" t="n">
-        <v>3.74</v>
+        <v>2.364</v>
       </c>
       <c r="H14" t="n">
-        <v>7.94</v>
+        <v>6.77</v>
       </c>
       <c r="I14" t="n">
-        <v>82.59999999999999</v>
+        <v>109.8</v>
       </c>
       <c r="J14" t="n">
-        <v>6.9</v>
+        <v>7.04</v>
       </c>
       <c r="K14" t="n">
-        <v>0.706</v>
+        <v>1.375</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>below-mid</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1213,52 +1213,106 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>lng</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.048</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H15" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="I15" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>below-mid</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>earnings-driven (tool&gt;cons)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>SBLK</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>whole-company</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>dry_bulk</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D16" t="n">
         <v>27.2</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E16" t="n">
         <v>6.9</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F16" t="n">
         <v>3.942</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G16" t="n">
         <v>5.035</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H16" t="n">
         <v>5.4</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I16" t="n">
         <v>27.7</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" t="n">
         <v>14.49</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K16" t="n">
         <v>1.225</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>elevated</t>
         </is>
       </c>
-      <c r="M15" t="n">
+      <c r="M16" t="n">
         <v>0.4</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>earnings-driven (tool&gt;cons)</t>
         </is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1159,7 +1159,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1169,32 +1169,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>17.25</v>
       </c>
       <c r="E14" t="n">
-        <v>14.2</v>
+        <v>10.5</v>
       </c>
       <c r="F14" t="n">
-        <v>1.127</v>
+        <v>1.643</v>
       </c>
       <c r="G14" t="n">
-        <v>2.364</v>
+        <v>3.892</v>
       </c>
       <c r="H14" t="n">
-        <v>6.77</v>
+        <v>4.43</v>
       </c>
       <c r="I14" t="n">
-        <v>109.8</v>
+        <v>136.9</v>
       </c>
       <c r="J14" t="n">
-        <v>7.04</v>
+        <v>9.52</v>
       </c>
       <c r="K14" t="n">
-        <v>1.375</v>
+        <v>1.208</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1223,40 +1223,40 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>29.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="F15" t="n">
-        <v>2.048</v>
+        <v>1.127</v>
       </c>
       <c r="G15" t="n">
-        <v>3.74</v>
+        <v>2.364</v>
       </c>
       <c r="H15" t="n">
-        <v>7.94</v>
+        <v>6.77</v>
       </c>
       <c r="I15" t="n">
-        <v>82.59999999999999</v>
+        <v>109.8</v>
       </c>
       <c r="J15" t="n">
-        <v>6.9</v>
+        <v>7.04</v>
       </c>
       <c r="K15" t="n">
-        <v>0.706</v>
+        <v>1.375</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>below-mid</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1267,52 +1267,106 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>lng</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.048</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H16" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="I16" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>below-mid</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>earnings-driven (tool&gt;cons)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>SBLK</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>whole-company</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>dry_bulk</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D17" t="n">
         <v>27.2</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E17" t="n">
         <v>6.9</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F17" t="n">
         <v>3.942</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G17" t="n">
         <v>5.035</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H17" t="n">
         <v>5.4</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I17" t="n">
         <v>27.7</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>14.49</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K17" t="n">
         <v>1.225</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>elevated</t>
         </is>
       </c>
-      <c r="M16" t="n">
+      <c r="M17" t="n">
         <v>0.4</v>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>earnings-driven (tool&gt;cons)</t>
         </is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1119,25 +1119,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>44</v>
+        <v>37.14</v>
       </c>
       <c r="E13" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>8.074</v>
       </c>
       <c r="G13" t="n">
         <v>19.883</v>
       </c>
       <c r="H13" t="n">
-        <v>2.21</v>
+        <v>1.87</v>
       </c>
       <c r="I13" t="n">
-        <v>148.5</v>
+        <v>146.3</v>
       </c>
       <c r="J13" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="K13" t="n">
         <v>1.978</v>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -565,7 +565,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -575,32 +575,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>28.2</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="n">
-        <v>9.5</v>
+        <v>11.1</v>
       </c>
       <c r="F3" t="n">
-        <v>2.968</v>
+        <v>1.099</v>
       </c>
       <c r="G3" t="n">
-        <v>9.494999999999999</v>
+        <v>3.602</v>
       </c>
       <c r="H3" t="n">
-        <v>2.97</v>
+        <v>3.39</v>
       </c>
       <c r="I3" t="n">
-        <v>219.9</v>
+        <v>227.7</v>
       </c>
       <c r="J3" t="n">
-        <v>10.53</v>
+        <v>9.01</v>
       </c>
       <c r="K3" t="n">
-        <v>1.691</v>
+        <v>2.497</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -629,40 +629,40 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.9</v>
+        <v>28.2</v>
       </c>
       <c r="E4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="F4" t="n">
-        <v>2.489</v>
+        <v>2.968</v>
       </c>
       <c r="G4" t="n">
-        <v>7.934</v>
+        <v>9.494999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>2.76</v>
+        <v>2.97</v>
       </c>
       <c r="I4" t="n">
-        <v>218.8</v>
+        <v>219.9</v>
       </c>
       <c r="J4" t="n">
-        <v>11.36</v>
+        <v>10.53</v>
       </c>
       <c r="K4" t="n">
-        <v>0.774</v>
+        <v>1.691</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>below-mid</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -673,50 +673,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid proxy)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>lng</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>21.9</v>
       </c>
       <c r="E5" t="n">
-        <v>11.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>6.842</v>
+        <v>2.489</v>
       </c>
       <c r="G5" t="n">
-        <v>21.722</v>
+        <v>7.934</v>
       </c>
       <c r="H5" t="n">
-        <v>3.59</v>
+        <v>2.76</v>
       </c>
       <c r="I5" t="n">
-        <v>217.5</v>
+        <v>218.8</v>
       </c>
       <c r="J5" t="n">
-        <v>8.77</v>
+        <v>11.36</v>
       </c>
       <c r="K5" t="n">
-        <v>2.145</v>
+        <v>0.774</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>below-mid</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -727,12 +727,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid proxy)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -741,28 +741,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>34.5</v>
+        <v>78</v>
       </c>
       <c r="E6" t="n">
-        <v>9.4</v>
+        <v>11.4</v>
       </c>
       <c r="F6" t="n">
-        <v>3.67</v>
+        <v>6.842</v>
       </c>
       <c r="G6" t="n">
-        <v>11.308</v>
+        <v>21.722</v>
       </c>
       <c r="H6" t="n">
-        <v>3.05</v>
+        <v>3.59</v>
       </c>
       <c r="I6" t="n">
-        <v>208.1</v>
+        <v>217.5</v>
       </c>
       <c r="J6" t="n">
-        <v>10.64</v>
+        <v>8.77</v>
       </c>
       <c r="K6" t="n">
-        <v>2.573</v>
+        <v>2.145</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -791,32 +791,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7.7</v>
+        <v>34.5</v>
       </c>
       <c r="E7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="F7" t="n">
-        <v>0.786</v>
+        <v>3.67</v>
       </c>
       <c r="G7" t="n">
-        <v>2.42</v>
+        <v>11.308</v>
       </c>
       <c r="H7" t="n">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="I7" t="n">
-        <v>208</v>
+        <v>208.1</v>
       </c>
       <c r="J7" t="n">
-        <v>10.2</v>
+        <v>10.64</v>
       </c>
       <c r="K7" t="n">
-        <v>1.665</v>
+        <v>2.573</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.4</v>
+        <v>7.7</v>
       </c>
       <c r="E8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>1.864</v>
+        <v>0.786</v>
       </c>
       <c r="G8" t="n">
-        <v>5.262</v>
+        <v>2.42</v>
       </c>
       <c r="H8" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="I8" t="n">
-        <v>182.4</v>
+        <v>208</v>
       </c>
       <c r="J8" t="n">
-        <v>11.36</v>
+        <v>10.2</v>
       </c>
       <c r="K8" t="n">
-        <v>2.788</v>
+        <v>1.665</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -903,28 +903,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>47.7</v>
+        <v>16.4</v>
       </c>
       <c r="E9" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>5.679</v>
+        <v>1.864</v>
       </c>
       <c r="G9" t="n">
-        <v>15.298</v>
+        <v>5.262</v>
       </c>
       <c r="H9" t="n">
         <v>3.12</v>
       </c>
       <c r="I9" t="n">
-        <v>169.4</v>
+        <v>182.4</v>
       </c>
       <c r="J9" t="n">
-        <v>11.9</v>
+        <v>11.36</v>
       </c>
       <c r="K9" t="n">
-        <v>2.515</v>
+        <v>2.788</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -953,32 +953,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>75.59999999999999</v>
+        <v>47.7</v>
       </c>
       <c r="E10" t="n">
-        <v>11.4</v>
+        <v>8.4</v>
       </c>
       <c r="F10" t="n">
-        <v>6.632</v>
+        <v>5.679</v>
       </c>
       <c r="G10" t="n">
-        <v>17.364</v>
+        <v>15.298</v>
       </c>
       <c r="H10" t="n">
-        <v>4.35</v>
+        <v>3.12</v>
       </c>
       <c r="I10" t="n">
-        <v>161.8</v>
+        <v>169.4</v>
       </c>
       <c r="J10" t="n">
-        <v>8.77</v>
+        <v>11.9</v>
       </c>
       <c r="K10" t="n">
-        <v>1.763</v>
+        <v>2.515</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1007,32 +1007,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>70.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>8.699999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="F11" t="n">
-        <v>8.138</v>
+        <v>6.632</v>
       </c>
       <c r="G11" t="n">
-        <v>21.127</v>
+        <v>17.364</v>
       </c>
       <c r="H11" t="n">
-        <v>3.35</v>
+        <v>4.35</v>
       </c>
       <c r="I11" t="n">
-        <v>159.6</v>
+        <v>161.8</v>
       </c>
       <c r="J11" t="n">
-        <v>11.49</v>
+        <v>8.77</v>
       </c>
       <c r="K11" t="n">
-        <v>2.153</v>
+        <v>1.763</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1061,40 +1061,40 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>24</v>
+        <v>70.8</v>
       </c>
       <c r="E12" t="n">
-        <v>13.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>1.727</v>
+        <v>8.138</v>
       </c>
       <c r="G12" t="n">
-        <v>4.293</v>
+        <v>21.127</v>
       </c>
       <c r="H12" t="n">
-        <v>5.59</v>
+        <v>3.35</v>
       </c>
       <c r="I12" t="n">
-        <v>148.6</v>
+        <v>159.6</v>
       </c>
       <c r="J12" t="n">
-        <v>7.19</v>
+        <v>11.49</v>
       </c>
       <c r="K12" t="n">
-        <v>1.144</v>
+        <v>2.153</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>mid-cycle</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1115,40 +1115,40 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>37.14</v>
+        <v>24</v>
       </c>
       <c r="E13" t="n">
-        <v>4.6</v>
+        <v>13.9</v>
       </c>
       <c r="F13" t="n">
-        <v>8.074</v>
+        <v>1.727</v>
       </c>
       <c r="G13" t="n">
-        <v>19.883</v>
+        <v>4.293</v>
       </c>
       <c r="H13" t="n">
-        <v>1.87</v>
+        <v>5.59</v>
       </c>
       <c r="I13" t="n">
-        <v>146.3</v>
+        <v>148.6</v>
       </c>
       <c r="J13" t="n">
-        <v>21.74</v>
+        <v>7.19</v>
       </c>
       <c r="K13" t="n">
-        <v>1.978</v>
+        <v>1.144</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>mid-cycle</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1169,40 +1169,40 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.25</v>
+        <v>37.14</v>
       </c>
       <c r="E14" t="n">
-        <v>10.5</v>
+        <v>4.6</v>
       </c>
       <c r="F14" t="n">
-        <v>1.643</v>
+        <v>8.074</v>
       </c>
       <c r="G14" t="n">
-        <v>3.892</v>
+        <v>19.883</v>
       </c>
       <c r="H14" t="n">
-        <v>4.43</v>
+        <v>1.87</v>
       </c>
       <c r="I14" t="n">
-        <v>136.9</v>
+        <v>146.3</v>
       </c>
       <c r="J14" t="n">
-        <v>9.52</v>
+        <v>21.74</v>
       </c>
       <c r="K14" t="n">
-        <v>1.208</v>
+        <v>1.978</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1223,32 +1223,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>17.25</v>
       </c>
       <c r="E15" t="n">
-        <v>14.2</v>
+        <v>10.5</v>
       </c>
       <c r="F15" t="n">
-        <v>1.127</v>
+        <v>1.643</v>
       </c>
       <c r="G15" t="n">
-        <v>2.364</v>
+        <v>3.892</v>
       </c>
       <c r="H15" t="n">
-        <v>6.77</v>
+        <v>4.43</v>
       </c>
       <c r="I15" t="n">
-        <v>109.8</v>
+        <v>136.9</v>
       </c>
       <c r="J15" t="n">
-        <v>7.04</v>
+        <v>9.52</v>
       </c>
       <c r="K15" t="n">
-        <v>1.375</v>
+        <v>1.208</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1277,40 +1277,40 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>29.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="F16" t="n">
-        <v>2.048</v>
+        <v>1.127</v>
       </c>
       <c r="G16" t="n">
-        <v>3.74</v>
+        <v>2.364</v>
       </c>
       <c r="H16" t="n">
-        <v>7.94</v>
+        <v>6.77</v>
       </c>
       <c r="I16" t="n">
-        <v>82.59999999999999</v>
+        <v>109.8</v>
       </c>
       <c r="J16" t="n">
-        <v>6.9</v>
+        <v>7.04</v>
       </c>
       <c r="K16" t="n">
-        <v>0.706</v>
+        <v>1.375</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>below-mid</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1321,52 +1321,106 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>lng</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.048</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H17" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="I17" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>below-mid</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>earnings-driven (tool&gt;cons)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>SBLK</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>whole-company</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>dry_bulk</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D18" t="n">
         <v>27.2</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E18" t="n">
         <v>6.9</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F18" t="n">
         <v>3.942</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G18" t="n">
         <v>5.035</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H18" t="n">
         <v>5.4</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I18" t="n">
         <v>27.7</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>14.49</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K18" t="n">
         <v>1.225</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>elevated</t>
         </is>
       </c>
-      <c r="M17" t="n">
+      <c r="M18" t="n">
         <v>0.4</v>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>earnings-driven (tool&gt;cons)</t>
         </is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1105,7 +1105,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1115,40 +1115,40 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>24</v>
+        <v>37.14</v>
       </c>
       <c r="E13" t="n">
-        <v>13.9</v>
+        <v>4.6</v>
       </c>
       <c r="F13" t="n">
-        <v>1.727</v>
+        <v>8.074</v>
       </c>
       <c r="G13" t="n">
-        <v>4.293</v>
+        <v>20.528</v>
       </c>
       <c r="H13" t="n">
-        <v>5.59</v>
+        <v>1.81</v>
       </c>
       <c r="I13" t="n">
-        <v>148.6</v>
+        <v>154.3</v>
       </c>
       <c r="J13" t="n">
-        <v>7.19</v>
+        <v>21.74</v>
       </c>
       <c r="K13" t="n">
-        <v>1.144</v>
+        <v>1.991</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>mid-cycle</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1169,40 +1169,40 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>37.14</v>
+        <v>24</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6</v>
+        <v>13.9</v>
       </c>
       <c r="F14" t="n">
-        <v>8.074</v>
+        <v>1.727</v>
       </c>
       <c r="G14" t="n">
-        <v>19.883</v>
+        <v>4.293</v>
       </c>
       <c r="H14" t="n">
-        <v>1.87</v>
+        <v>5.59</v>
       </c>
       <c r="I14" t="n">
-        <v>146.3</v>
+        <v>148.6</v>
       </c>
       <c r="J14" t="n">
-        <v>21.74</v>
+        <v>7.19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.978</v>
+        <v>1.144</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>mid-cycle</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
@@ -1375,7 +1375,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1385,32 +1385,32 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>containerships</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>27.2</v>
+        <v>2.78</v>
       </c>
       <c r="E18" t="n">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>3.942</v>
+        <v>0.347</v>
       </c>
       <c r="G18" t="n">
-        <v>5.035</v>
+        <v>0.537</v>
       </c>
       <c r="H18" t="n">
-        <v>5.4</v>
+        <v>5.18</v>
       </c>
       <c r="I18" t="n">
-        <v>27.7</v>
+        <v>54.6</v>
       </c>
       <c r="J18" t="n">
-        <v>14.49</v>
+        <v>12.5</v>
       </c>
       <c r="K18" t="n">
-        <v>1.225</v>
+        <v>1.206</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1421,6 +1421,114 @@
         <v>0.4</v>
       </c>
       <c r="N18" t="inlineStr">
+        <is>
+          <t>earnings-driven (tool&gt;cons)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>containerships</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10.261</v>
+      </c>
+      <c r="G19" t="n">
+        <v>14.044</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I19" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.453</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>elevated</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>earnings-driven (tool&gt;cons)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>dry_bulk</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.942</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5.035</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>elevated</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>earnings-driven (tool&gt;cons)</t>
         </is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -565,7 +565,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -579,28 +579,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>5.4</v>
       </c>
       <c r="E3" t="n">
-        <v>11.1</v>
+        <v>22</v>
       </c>
       <c r="F3" t="n">
-        <v>1.099</v>
+        <v>0.245</v>
       </c>
       <c r="G3" t="n">
-        <v>3.602</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>3.39</v>
+        <v>5.4</v>
       </c>
       <c r="I3" t="n">
-        <v>227.7</v>
+        <v>307.5</v>
       </c>
       <c r="J3" t="n">
-        <v>9.01</v>
+        <v>4.55</v>
       </c>
       <c r="K3" t="n">
-        <v>2.497</v>
+        <v>2.788</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -629,32 +629,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>28.2</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="n">
-        <v>9.5</v>
+        <v>11.1</v>
       </c>
       <c r="F4" t="n">
-        <v>2.968</v>
+        <v>1.099</v>
       </c>
       <c r="G4" t="n">
-        <v>9.494999999999999</v>
+        <v>3.602</v>
       </c>
       <c r="H4" t="n">
-        <v>2.97</v>
+        <v>3.39</v>
       </c>
       <c r="I4" t="n">
-        <v>219.9</v>
+        <v>227.7</v>
       </c>
       <c r="J4" t="n">
-        <v>10.53</v>
+        <v>9.01</v>
       </c>
       <c r="K4" t="n">
-        <v>1.691</v>
+        <v>2.497</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -683,40 +683,40 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21.9</v>
+        <v>28.2</v>
       </c>
       <c r="E5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="F5" t="n">
-        <v>2.489</v>
+        <v>2.968</v>
       </c>
       <c r="G5" t="n">
-        <v>7.934</v>
+        <v>9.494999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>2.76</v>
+        <v>2.97</v>
       </c>
       <c r="I5" t="n">
-        <v>218.8</v>
+        <v>219.9</v>
       </c>
       <c r="J5" t="n">
-        <v>11.36</v>
+        <v>10.53</v>
       </c>
       <c r="K5" t="n">
-        <v>0.774</v>
+        <v>1.691</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>below-mid</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -727,50 +727,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid proxy)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>lng</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>78</v>
+        <v>21.9</v>
       </c>
       <c r="E6" t="n">
-        <v>11.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>6.842</v>
+        <v>2.489</v>
       </c>
       <c r="G6" t="n">
-        <v>21.722</v>
+        <v>7.934</v>
       </c>
       <c r="H6" t="n">
-        <v>3.59</v>
+        <v>2.76</v>
       </c>
       <c r="I6" t="n">
-        <v>217.5</v>
+        <v>218.8</v>
       </c>
       <c r="J6" t="n">
-        <v>8.77</v>
+        <v>11.36</v>
       </c>
       <c r="K6" t="n">
-        <v>2.145</v>
+        <v>0.774</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>below-mid</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -781,12 +781,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid proxy)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -795,28 +795,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>34.5</v>
+        <v>78</v>
       </c>
       <c r="E7" t="n">
-        <v>9.4</v>
+        <v>11.4</v>
       </c>
       <c r="F7" t="n">
-        <v>3.67</v>
+        <v>6.842</v>
       </c>
       <c r="G7" t="n">
-        <v>11.308</v>
+        <v>21.722</v>
       </c>
       <c r="H7" t="n">
-        <v>3.05</v>
+        <v>3.59</v>
       </c>
       <c r="I7" t="n">
-        <v>208.1</v>
+        <v>217.5</v>
       </c>
       <c r="J7" t="n">
-        <v>10.64</v>
+        <v>8.77</v>
       </c>
       <c r="K7" t="n">
-        <v>2.573</v>
+        <v>2.145</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7.7</v>
+        <v>34.5</v>
       </c>
       <c r="E8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="F8" t="n">
-        <v>0.786</v>
+        <v>3.67</v>
       </c>
       <c r="G8" t="n">
-        <v>2.42</v>
+        <v>11.308</v>
       </c>
       <c r="H8" t="n">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="I8" t="n">
-        <v>208</v>
+        <v>208.1</v>
       </c>
       <c r="J8" t="n">
-        <v>10.2</v>
+        <v>10.64</v>
       </c>
       <c r="K8" t="n">
-        <v>1.665</v>
+        <v>2.573</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -899,32 +899,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.4</v>
+        <v>7.7</v>
       </c>
       <c r="E9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>1.864</v>
+        <v>0.786</v>
       </c>
       <c r="G9" t="n">
-        <v>5.262</v>
+        <v>2.42</v>
       </c>
       <c r="H9" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="I9" t="n">
-        <v>182.4</v>
+        <v>208</v>
       </c>
       <c r="J9" t="n">
-        <v>11.36</v>
+        <v>10.2</v>
       </c>
       <c r="K9" t="n">
-        <v>2.788</v>
+        <v>1.665</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -957,28 +957,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.7</v>
+        <v>16.4</v>
       </c>
       <c r="E10" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>5.679</v>
+        <v>1.864</v>
       </c>
       <c r="G10" t="n">
-        <v>15.298</v>
+        <v>5.262</v>
       </c>
       <c r="H10" t="n">
         <v>3.12</v>
       </c>
       <c r="I10" t="n">
-        <v>169.4</v>
+        <v>182.4</v>
       </c>
       <c r="J10" t="n">
-        <v>11.9</v>
+        <v>11.36</v>
       </c>
       <c r="K10" t="n">
-        <v>2.515</v>
+        <v>2.788</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1007,32 +1007,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>75.59999999999999</v>
+        <v>47.7</v>
       </c>
       <c r="E11" t="n">
-        <v>11.4</v>
+        <v>8.4</v>
       </c>
       <c r="F11" t="n">
-        <v>6.632</v>
+        <v>5.679</v>
       </c>
       <c r="G11" t="n">
-        <v>17.364</v>
+        <v>15.298</v>
       </c>
       <c r="H11" t="n">
-        <v>4.35</v>
+        <v>3.12</v>
       </c>
       <c r="I11" t="n">
-        <v>161.8</v>
+        <v>169.4</v>
       </c>
       <c r="J11" t="n">
-        <v>8.77</v>
+        <v>11.9</v>
       </c>
       <c r="K11" t="n">
-        <v>1.763</v>
+        <v>2.515</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1061,32 +1061,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>70.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>8.699999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="F12" t="n">
-        <v>8.138</v>
+        <v>6.632</v>
       </c>
       <c r="G12" t="n">
-        <v>21.127</v>
+        <v>17.364</v>
       </c>
       <c r="H12" t="n">
-        <v>3.35</v>
+        <v>4.35</v>
       </c>
       <c r="I12" t="n">
-        <v>159.6</v>
+        <v>161.8</v>
       </c>
       <c r="J12" t="n">
-        <v>11.49</v>
+        <v>8.77</v>
       </c>
       <c r="K12" t="n">
-        <v>2.153</v>
+        <v>1.763</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1119,28 +1119,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>37.14</v>
+        <v>70.8</v>
       </c>
       <c r="E13" t="n">
-        <v>4.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>8.074</v>
+        <v>8.138</v>
       </c>
       <c r="G13" t="n">
-        <v>20.528</v>
+        <v>21.127</v>
       </c>
       <c r="H13" t="n">
-        <v>1.81</v>
+        <v>3.35</v>
       </c>
       <c r="I13" t="n">
-        <v>154.3</v>
+        <v>159.6</v>
       </c>
       <c r="J13" t="n">
-        <v>21.74</v>
+        <v>11.49</v>
       </c>
       <c r="K13" t="n">
-        <v>1.991</v>
+        <v>2.153</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1169,40 +1169,40 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>24</v>
+        <v>37.14</v>
       </c>
       <c r="E14" t="n">
-        <v>13.9</v>
+        <v>4.6</v>
       </c>
       <c r="F14" t="n">
-        <v>1.727</v>
+        <v>8.074</v>
       </c>
       <c r="G14" t="n">
-        <v>4.293</v>
+        <v>20.528</v>
       </c>
       <c r="H14" t="n">
-        <v>5.59</v>
+        <v>1.81</v>
       </c>
       <c r="I14" t="n">
-        <v>148.6</v>
+        <v>154.3</v>
       </c>
       <c r="J14" t="n">
-        <v>7.19</v>
+        <v>21.74</v>
       </c>
       <c r="K14" t="n">
-        <v>1.144</v>
+        <v>1.991</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>mid-cycle</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1227,36 +1227,36 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17.25</v>
+        <v>24</v>
       </c>
       <c r="E15" t="n">
-        <v>10.5</v>
+        <v>13.9</v>
       </c>
       <c r="F15" t="n">
-        <v>1.643</v>
+        <v>1.727</v>
       </c>
       <c r="G15" t="n">
-        <v>3.892</v>
+        <v>4.293</v>
       </c>
       <c r="H15" t="n">
-        <v>4.43</v>
+        <v>5.59</v>
       </c>
       <c r="I15" t="n">
-        <v>136.9</v>
+        <v>148.6</v>
       </c>
       <c r="J15" t="n">
-        <v>9.52</v>
+        <v>7.19</v>
       </c>
       <c r="K15" t="n">
-        <v>1.208</v>
+        <v>1.144</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>mid-cycle</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1277,32 +1277,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>17.25</v>
       </c>
       <c r="E16" t="n">
-        <v>14.2</v>
+        <v>10.5</v>
       </c>
       <c r="F16" t="n">
-        <v>1.127</v>
+        <v>1.643</v>
       </c>
       <c r="G16" t="n">
-        <v>2.364</v>
+        <v>3.892</v>
       </c>
       <c r="H16" t="n">
-        <v>6.77</v>
+        <v>4.43</v>
       </c>
       <c r="I16" t="n">
-        <v>109.8</v>
+        <v>136.9</v>
       </c>
       <c r="J16" t="n">
-        <v>7.04</v>
+        <v>9.52</v>
       </c>
       <c r="K16" t="n">
-        <v>1.375</v>
+        <v>1.208</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1331,40 +1331,40 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>29.7</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="F17" t="n">
-        <v>2.048</v>
+        <v>1.127</v>
       </c>
       <c r="G17" t="n">
-        <v>3.74</v>
+        <v>2.364</v>
       </c>
       <c r="H17" t="n">
-        <v>7.94</v>
+        <v>6.77</v>
       </c>
       <c r="I17" t="n">
-        <v>82.59999999999999</v>
+        <v>109.8</v>
       </c>
       <c r="J17" t="n">
-        <v>6.9</v>
+        <v>7.04</v>
       </c>
       <c r="K17" t="n">
-        <v>0.706</v>
+        <v>1.375</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>below-mid</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1385,40 +1385,40 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>containerships</t>
+          <t>lng</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.78</v>
+        <v>29.7</v>
       </c>
       <c r="E18" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="F18" t="n">
-        <v>0.347</v>
+        <v>2.048</v>
       </c>
       <c r="G18" t="n">
-        <v>0.537</v>
+        <v>3.74</v>
       </c>
       <c r="H18" t="n">
-        <v>5.18</v>
+        <v>7.94</v>
       </c>
       <c r="I18" t="n">
-        <v>54.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>12.5</v>
+        <v>6.9</v>
       </c>
       <c r="K18" t="n">
-        <v>1.206</v>
+        <v>0.706</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>below-mid</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1443,28 +1443,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>38.99</v>
+        <v>2.78</v>
       </c>
       <c r="E19" t="n">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>10.261</v>
+        <v>0.347</v>
       </c>
       <c r="G19" t="n">
-        <v>14.044</v>
+        <v>0.537</v>
       </c>
       <c r="H19" t="n">
-        <v>2.78</v>
+        <v>5.18</v>
       </c>
       <c r="I19" t="n">
-        <v>36.9</v>
+        <v>54.6</v>
       </c>
       <c r="J19" t="n">
-        <v>26.32</v>
+        <v>12.5</v>
       </c>
       <c r="K19" t="n">
-        <v>1.453</v>
+        <v>1.206</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>containerships</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>27.2</v>
+        <v>38.99</v>
       </c>
       <c r="E20" t="n">
-        <v>6.9</v>
+        <v>3.8</v>
       </c>
       <c r="F20" t="n">
-        <v>3.942</v>
+        <v>10.261</v>
       </c>
       <c r="G20" t="n">
-        <v>5.035</v>
+        <v>14.044</v>
       </c>
       <c r="H20" t="n">
-        <v>5.4</v>
+        <v>2.78</v>
       </c>
       <c r="I20" t="n">
-        <v>27.7</v>
+        <v>36.9</v>
       </c>
       <c r="J20" t="n">
-        <v>14.49</v>
+        <v>26.32</v>
       </c>
       <c r="K20" t="n">
-        <v>1.225</v>
+        <v>1.453</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1529,6 +1529,60 @@
         <v>0.4</v>
       </c>
       <c r="N20" t="inlineStr">
+        <is>
+          <t>earnings-driven (tool&gt;cons)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>dry_bulk</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.942</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5.035</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>elevated</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>earnings-driven (tool&gt;cons)</t>
         </is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -654,7 +654,7 @@
         <v>9.01</v>
       </c>
       <c r="K4" t="n">
-        <v>2.497</v>
+        <v>2.459</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>8.77</v>
       </c>
       <c r="K7" t="n">
-        <v>2.145</v>
+        <v>2.111</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>11.49</v>
       </c>
       <c r="K13" t="n">
-        <v>2.153</v>
+        <v>1.909</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>21.74</v>
       </c>
       <c r="K14" t="n">
-        <v>1.991</v>
+        <v>1.806</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1267,7 +1267,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1277,40 +1277,40 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17.25</v>
+        <v>14.9</v>
       </c>
       <c r="E16" t="n">
-        <v>10.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>1.643</v>
+        <v>1.536</v>
       </c>
       <c r="G16" t="n">
-        <v>3.892</v>
+        <v>3.675</v>
       </c>
       <c r="H16" t="n">
-        <v>4.43</v>
+        <v>4.05</v>
       </c>
       <c r="I16" t="n">
-        <v>136.9</v>
+        <v>139.3</v>
       </c>
       <c r="J16" t="n">
-        <v>9.52</v>
+        <v>10.31</v>
       </c>
       <c r="K16" t="n">
-        <v>1.208</v>
+        <v>1.537</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>17.25</v>
       </c>
       <c r="E17" t="n">
-        <v>14.2</v>
+        <v>10.5</v>
       </c>
       <c r="F17" t="n">
-        <v>1.127</v>
+        <v>1.643</v>
       </c>
       <c r="G17" t="n">
-        <v>2.364</v>
+        <v>3.892</v>
       </c>
       <c r="H17" t="n">
-        <v>6.77</v>
+        <v>4.43</v>
       </c>
       <c r="I17" t="n">
-        <v>109.8</v>
+        <v>136.9</v>
       </c>
       <c r="J17" t="n">
-        <v>7.04</v>
+        <v>9.52</v>
       </c>
       <c r="K17" t="n">
-        <v>1.375</v>
+        <v>1.208</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1385,40 +1385,40 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>29.7</v>
+        <v>16</v>
       </c>
       <c r="E18" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="F18" t="n">
-        <v>2.048</v>
+        <v>1.127</v>
       </c>
       <c r="G18" t="n">
-        <v>3.74</v>
+        <v>2.364</v>
       </c>
       <c r="H18" t="n">
-        <v>7.94</v>
+        <v>6.77</v>
       </c>
       <c r="I18" t="n">
-        <v>82.59999999999999</v>
+        <v>109.8</v>
       </c>
       <c r="J18" t="n">
-        <v>6.9</v>
+        <v>7.04</v>
       </c>
       <c r="K18" t="n">
-        <v>0.706</v>
+        <v>1.375</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>below-mid</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1439,40 +1439,40 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>containerships</t>
+          <t>lng</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.78</v>
+        <v>29.7</v>
       </c>
       <c r="E19" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="F19" t="n">
-        <v>0.347</v>
+        <v>2.048</v>
       </c>
       <c r="G19" t="n">
-        <v>0.537</v>
+        <v>3.74</v>
       </c>
       <c r="H19" t="n">
-        <v>5.18</v>
+        <v>7.94</v>
       </c>
       <c r="I19" t="n">
-        <v>54.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>12.5</v>
+        <v>6.9</v>
       </c>
       <c r="K19" t="n">
-        <v>1.206</v>
+        <v>0.706</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>below-mid</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1497,28 +1497,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>38.99</v>
+        <v>2.78</v>
       </c>
       <c r="E20" t="n">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>10.261</v>
+        <v>0.347</v>
       </c>
       <c r="G20" t="n">
-        <v>14.044</v>
+        <v>0.537</v>
       </c>
       <c r="H20" t="n">
-        <v>2.78</v>
+        <v>5.18</v>
       </c>
       <c r="I20" t="n">
-        <v>36.9</v>
+        <v>54.6</v>
       </c>
       <c r="J20" t="n">
-        <v>26.32</v>
+        <v>12.5</v>
       </c>
       <c r="K20" t="n">
-        <v>1.453</v>
+        <v>1.206</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1547,32 +1547,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>containerships</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>27.2</v>
+        <v>38.99</v>
       </c>
       <c r="E21" t="n">
-        <v>6.9</v>
+        <v>3.8</v>
       </c>
       <c r="F21" t="n">
-        <v>3.942</v>
+        <v>10.261</v>
       </c>
       <c r="G21" t="n">
-        <v>5.035</v>
+        <v>14.044</v>
       </c>
       <c r="H21" t="n">
-        <v>5.4</v>
+        <v>2.78</v>
       </c>
       <c r="I21" t="n">
-        <v>27.7</v>
+        <v>36.9</v>
       </c>
       <c r="J21" t="n">
-        <v>14.49</v>
+        <v>26.32</v>
       </c>
       <c r="K21" t="n">
-        <v>1.225</v>
+        <v>1.453</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1583,6 +1583,60 @@
         <v>0.4</v>
       </c>
       <c r="N21" t="inlineStr">
+        <is>
+          <t>earnings-driven (tool&gt;cons)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>dry_bulk</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3.942</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5.035</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="J22" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>elevated</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>earnings-driven (tool&gt;cons)</t>
         </is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1302,7 +1302,7 @@
         <v>10.31</v>
       </c>
       <c r="K16" t="n">
-        <v>1.537</v>
+        <v>1.518</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>9.52</v>
       </c>
       <c r="K17" t="n">
-        <v>1.208</v>
+        <v>1.209</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>14.49</v>
       </c>
       <c r="K22" t="n">
-        <v>1.225</v>
+        <v>1.224</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1375,7 +1375,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1385,32 +1385,32 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>6.39</v>
       </c>
       <c r="E18" t="n">
-        <v>14.2</v>
+        <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>1.127</v>
+        <v>0.799</v>
       </c>
       <c r="G18" t="n">
-        <v>2.364</v>
+        <v>1.807</v>
       </c>
       <c r="H18" t="n">
-        <v>6.77</v>
+        <v>3.54</v>
       </c>
       <c r="I18" t="n">
-        <v>109.8</v>
+        <v>126.3</v>
       </c>
       <c r="J18" t="n">
-        <v>7.04</v>
+        <v>12.5</v>
       </c>
       <c r="K18" t="n">
-        <v>1.375</v>
+        <v>1.403</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1439,40 +1439,40 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>29.7</v>
+        <v>16</v>
       </c>
       <c r="E19" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="F19" t="n">
-        <v>2.048</v>
+        <v>1.127</v>
       </c>
       <c r="G19" t="n">
-        <v>3.74</v>
+        <v>2.364</v>
       </c>
       <c r="H19" t="n">
-        <v>7.94</v>
+        <v>6.77</v>
       </c>
       <c r="I19" t="n">
-        <v>82.59999999999999</v>
+        <v>109.8</v>
       </c>
       <c r="J19" t="n">
-        <v>6.9</v>
+        <v>7.04</v>
       </c>
       <c r="K19" t="n">
-        <v>0.706</v>
+        <v>1.375</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>below-mid</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1493,40 +1493,40 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>containerships</t>
+          <t>lng</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.78</v>
+        <v>29.7</v>
       </c>
       <c r="E20" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="F20" t="n">
-        <v>0.347</v>
+        <v>2.048</v>
       </c>
       <c r="G20" t="n">
-        <v>0.537</v>
+        <v>3.74</v>
       </c>
       <c r="H20" t="n">
-        <v>5.18</v>
+        <v>7.94</v>
       </c>
       <c r="I20" t="n">
-        <v>54.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>12.5</v>
+        <v>6.9</v>
       </c>
       <c r="K20" t="n">
-        <v>1.206</v>
+        <v>0.706</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>below-mid</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1551,28 +1551,28 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>38.99</v>
+        <v>2.78</v>
       </c>
       <c r="E21" t="n">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>10.261</v>
+        <v>0.347</v>
       </c>
       <c r="G21" t="n">
-        <v>14.044</v>
+        <v>0.537</v>
       </c>
       <c r="H21" t="n">
-        <v>2.78</v>
+        <v>5.18</v>
       </c>
       <c r="I21" t="n">
-        <v>36.9</v>
+        <v>54.6</v>
       </c>
       <c r="J21" t="n">
-        <v>26.32</v>
+        <v>12.5</v>
       </c>
       <c r="K21" t="n">
-        <v>1.453</v>
+        <v>1.206</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1601,32 +1601,32 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>containerships</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>27.2</v>
+        <v>38.99</v>
       </c>
       <c r="E22" t="n">
-        <v>6.9</v>
+        <v>3.8</v>
       </c>
       <c r="F22" t="n">
-        <v>3.942</v>
+        <v>10.261</v>
       </c>
       <c r="G22" t="n">
-        <v>5.035</v>
+        <v>14.044</v>
       </c>
       <c r="H22" t="n">
-        <v>5.4</v>
+        <v>2.78</v>
       </c>
       <c r="I22" t="n">
-        <v>27.7</v>
+        <v>36.9</v>
       </c>
       <c r="J22" t="n">
-        <v>14.49</v>
+        <v>26.32</v>
       </c>
       <c r="K22" t="n">
-        <v>1.224</v>
+        <v>1.453</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1637,6 +1637,60 @@
         <v>0.4</v>
       </c>
       <c r="N22" t="inlineStr">
+        <is>
+          <t>earnings-driven (tool&gt;cons)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>dry_bulk</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.942</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5.035</v>
+      </c>
+      <c r="H23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="J23" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.224</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>elevated</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>earnings-driven (tool&gt;cons)</t>
         </is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1398,13 +1398,13 @@
         <v>0.799</v>
       </c>
       <c r="G18" t="n">
-        <v>1.807</v>
+        <v>1.742</v>
       </c>
       <c r="H18" t="n">
-        <v>3.54</v>
+        <v>3.67</v>
       </c>
       <c r="I18" t="n">
-        <v>126.3</v>
+        <v>118</v>
       </c>
       <c r="J18" t="n">
         <v>12.5</v>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -654,7 +654,7 @@
         <v>9.01</v>
       </c>
       <c r="K4" t="n">
-        <v>2.459</v>
+        <v>2.434</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>10.64</v>
       </c>
       <c r="K8" t="n">
-        <v>2.573</v>
+        <v>2.564</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>11.9</v>
       </c>
       <c r="K11" t="n">
-        <v>2.515</v>
+        <v>2.521</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>21.74</v>
       </c>
       <c r="K14" t="n">
-        <v>1.806</v>
+        <v>1.802</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1302,15 +1302,15 @@
         <v>10.31</v>
       </c>
       <c r="K16" t="n">
-        <v>1.518</v>
+        <v>1.495</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>12.5</v>
       </c>
       <c r="K18" t="n">
-        <v>1.403</v>
+        <v>1.405</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -654,7 +654,7 @@
         <v>9.01</v>
       </c>
       <c r="K4" t="n">
-        <v>2.434</v>
+        <v>2.453</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>10.64</v>
       </c>
       <c r="K8" t="n">
-        <v>2.564</v>
+        <v>2.573</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>11.9</v>
       </c>
       <c r="K11" t="n">
-        <v>2.521</v>
+        <v>2.511</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>21.74</v>
       </c>
       <c r="K14" t="n">
-        <v>1.802</v>
+        <v>1.806</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1302,15 +1302,15 @@
         <v>10.31</v>
       </c>
       <c r="K16" t="n">
-        <v>1.495</v>
+        <v>1.513</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1105,7 +1105,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1115,40 +1115,40 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>70.8</v>
+        <v>6.39</v>
       </c>
       <c r="E13" t="n">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>8.138</v>
+        <v>0.799</v>
       </c>
       <c r="G13" t="n">
-        <v>21.127</v>
+        <v>2.091</v>
       </c>
       <c r="H13" t="n">
-        <v>3.35</v>
+        <v>3.06</v>
       </c>
       <c r="I13" t="n">
-        <v>159.6</v>
+        <v>161.8</v>
       </c>
       <c r="J13" t="n">
-        <v>11.49</v>
+        <v>12.5</v>
       </c>
       <c r="K13" t="n">
-        <v>1.909</v>
+        <v>1.42</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1173,28 +1173,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>37.14</v>
+        <v>70.8</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>8.074</v>
+        <v>8.138</v>
       </c>
       <c r="G14" t="n">
-        <v>20.528</v>
+        <v>21.127</v>
       </c>
       <c r="H14" t="n">
-        <v>1.81</v>
+        <v>3.35</v>
       </c>
       <c r="I14" t="n">
-        <v>154.3</v>
+        <v>159.6</v>
       </c>
       <c r="J14" t="n">
-        <v>21.74</v>
+        <v>11.49</v>
       </c>
       <c r="K14" t="n">
-        <v>1.806</v>
+        <v>1.909</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1223,40 +1223,40 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>24</v>
+        <v>37.14</v>
       </c>
       <c r="E15" t="n">
-        <v>13.9</v>
+        <v>4.6</v>
       </c>
       <c r="F15" t="n">
-        <v>1.727</v>
+        <v>8.074</v>
       </c>
       <c r="G15" t="n">
-        <v>4.293</v>
+        <v>20.528</v>
       </c>
       <c r="H15" t="n">
-        <v>5.59</v>
+        <v>1.81</v>
       </c>
       <c r="I15" t="n">
-        <v>148.6</v>
+        <v>154.3</v>
       </c>
       <c r="J15" t="n">
-        <v>7.19</v>
+        <v>21.74</v>
       </c>
       <c r="K15" t="n">
-        <v>1.144</v>
+        <v>1.806</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>mid-cycle</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1277,40 +1277,40 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.9</v>
+        <v>24</v>
       </c>
       <c r="E16" t="n">
-        <v>9.699999999999999</v>
+        <v>13.9</v>
       </c>
       <c r="F16" t="n">
-        <v>1.536</v>
+        <v>1.727</v>
       </c>
       <c r="G16" t="n">
-        <v>3.675</v>
+        <v>4.293</v>
       </c>
       <c r="H16" t="n">
-        <v>4.05</v>
+        <v>5.59</v>
       </c>
       <c r="I16" t="n">
-        <v>139.3</v>
+        <v>148.6</v>
       </c>
       <c r="J16" t="n">
-        <v>10.31</v>
+        <v>7.19</v>
       </c>
       <c r="K16" t="n">
-        <v>1.513</v>
+        <v>1.144</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>mid-cycle</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1331,40 +1331,40 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17.25</v>
+        <v>14.9</v>
       </c>
       <c r="E17" t="n">
-        <v>10.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>1.643</v>
+        <v>1.536</v>
       </c>
       <c r="G17" t="n">
-        <v>3.892</v>
+        <v>3.675</v>
       </c>
       <c r="H17" t="n">
-        <v>4.43</v>
+        <v>4.05</v>
       </c>
       <c r="I17" t="n">
-        <v>136.9</v>
+        <v>139.3</v>
       </c>
       <c r="J17" t="n">
-        <v>9.52</v>
+        <v>10.31</v>
       </c>
       <c r="K17" t="n">
-        <v>1.209</v>
+        <v>1.513</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1389,28 +1389,28 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6.39</v>
+        <v>17.25</v>
       </c>
       <c r="E18" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="F18" t="n">
-        <v>0.799</v>
+        <v>1.643</v>
       </c>
       <c r="G18" t="n">
-        <v>1.742</v>
+        <v>3.892</v>
       </c>
       <c r="H18" t="n">
-        <v>3.67</v>
+        <v>4.43</v>
       </c>
       <c r="I18" t="n">
-        <v>118</v>
+        <v>136.9</v>
       </c>
       <c r="J18" t="n">
-        <v>12.5</v>
+        <v>9.52</v>
       </c>
       <c r="K18" t="n">
-        <v>1.405</v>
+        <v>1.209</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1668,19 +1668,19 @@
         <v>3.942</v>
       </c>
       <c r="G23" t="n">
-        <v>5.035</v>
+        <v>5.363</v>
       </c>
       <c r="H23" t="n">
-        <v>5.4</v>
+        <v>5.07</v>
       </c>
       <c r="I23" t="n">
-        <v>27.7</v>
+        <v>36</v>
       </c>
       <c r="J23" t="n">
         <v>14.49</v>
       </c>
       <c r="K23" t="n">
-        <v>1.224</v>
+        <v>1.247</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -654,7 +654,7 @@
         <v>9.01</v>
       </c>
       <c r="K4" t="n">
-        <v>2.453</v>
+        <v>2.454</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -966,13 +966,13 @@
         <v>1.864</v>
       </c>
       <c r="G10" t="n">
-        <v>5.262</v>
+        <v>5.514</v>
       </c>
       <c r="H10" t="n">
-        <v>3.12</v>
+        <v>2.97</v>
       </c>
       <c r="I10" t="n">
-        <v>182.4</v>
+        <v>195.9</v>
       </c>
       <c r="J10" t="n">
         <v>11.36</v>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -534,13 +534,13 @@
         <v>0.302</v>
       </c>
       <c r="G2" t="n">
-        <v>1.698</v>
+        <v>1.452</v>
       </c>
       <c r="H2" t="n">
-        <v>3.06</v>
+        <v>3.58</v>
       </c>
       <c r="I2" t="n">
-        <v>461.7</v>
+        <v>380.2</v>
       </c>
       <c r="J2" t="n">
         <v>5.81</v>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1051,7 +1051,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1061,40 +1061,40 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>75.59999999999999</v>
+        <v>6.39</v>
       </c>
       <c r="E12" t="n">
-        <v>11.4</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
-        <v>6.632</v>
+        <v>0.799</v>
       </c>
       <c r="G12" t="n">
-        <v>17.364</v>
+        <v>2.134</v>
       </c>
       <c r="H12" t="n">
-        <v>4.35</v>
+        <v>2.99</v>
       </c>
       <c r="I12" t="n">
-        <v>161.8</v>
+        <v>167.2</v>
       </c>
       <c r="J12" t="n">
-        <v>8.77</v>
+        <v>12.5</v>
       </c>
       <c r="K12" t="n">
-        <v>1.763</v>
+        <v>1.419</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1115,40 +1115,40 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6.39</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>11.4</v>
       </c>
       <c r="F13" t="n">
-        <v>0.799</v>
+        <v>6.632</v>
       </c>
       <c r="G13" t="n">
-        <v>2.091</v>
+        <v>17.364</v>
       </c>
       <c r="H13" t="n">
-        <v>3.06</v>
+        <v>4.35</v>
       </c>
       <c r="I13" t="n">
         <v>161.8</v>
       </c>
       <c r="J13" t="n">
-        <v>12.5</v>
+        <v>8.77</v>
       </c>
       <c r="K13" t="n">
-        <v>1.42</v>
+        <v>1.763</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1452,13 +1452,13 @@
         <v>1.127</v>
       </c>
       <c r="G19" t="n">
-        <v>2.364</v>
+        <v>2.221</v>
       </c>
       <c r="H19" t="n">
-        <v>6.77</v>
+        <v>7.2</v>
       </c>
       <c r="I19" t="n">
-        <v>109.8</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J19" t="n">
         <v>7.04</v>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -594,7 +594,7 @@
         <v>5.4</v>
       </c>
       <c r="I3" t="n">
-        <v>307.5</v>
+        <v>307.3</v>
       </c>
       <c r="J3" t="n">
         <v>4.55</v>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -912,13 +912,13 @@
         <v>0.786</v>
       </c>
       <c r="G9" t="n">
-        <v>2.42</v>
+        <v>2.395</v>
       </c>
       <c r="H9" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="I9" t="n">
-        <v>208</v>
+        <v>204.8</v>
       </c>
       <c r="J9" t="n">
         <v>10.2</v>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1105,7 +1105,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1115,32 +1115,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>75.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="E13" t="n">
-        <v>11.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>6.632</v>
+        <v>8.138</v>
       </c>
       <c r="G13" t="n">
-        <v>17.364</v>
+        <v>21.127</v>
       </c>
       <c r="H13" t="n">
-        <v>4.35</v>
+        <v>3.35</v>
       </c>
       <c r="I13" t="n">
-        <v>161.8</v>
+        <v>159.6</v>
       </c>
       <c r="J13" t="n">
-        <v>8.77</v>
+        <v>11.49</v>
       </c>
       <c r="K13" t="n">
-        <v>1.763</v>
+        <v>1.909</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1173,28 +1173,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>70.8</v>
+        <v>37.14</v>
       </c>
       <c r="E14" t="n">
-        <v>8.699999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="F14" t="n">
-        <v>8.138</v>
+        <v>8.074</v>
       </c>
       <c r="G14" t="n">
-        <v>21.127</v>
+        <v>20.528</v>
       </c>
       <c r="H14" t="n">
-        <v>3.35</v>
+        <v>1.81</v>
       </c>
       <c r="I14" t="n">
-        <v>159.6</v>
+        <v>154.3</v>
       </c>
       <c r="J14" t="n">
-        <v>11.49</v>
+        <v>21.74</v>
       </c>
       <c r="K14" t="n">
-        <v>1.909</v>
+        <v>1.806</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1223,32 +1223,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>37.14</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6</v>
+        <v>11.4</v>
       </c>
       <c r="F15" t="n">
-        <v>8.074</v>
+        <v>6.632</v>
       </c>
       <c r="G15" t="n">
-        <v>20.528</v>
+        <v>16.662</v>
       </c>
       <c r="H15" t="n">
-        <v>1.81</v>
+        <v>4.54</v>
       </c>
       <c r="I15" t="n">
-        <v>154.3</v>
+        <v>151.2</v>
       </c>
       <c r="J15" t="n">
-        <v>21.74</v>
+        <v>8.77</v>
       </c>
       <c r="K15" t="n">
-        <v>1.806</v>
+        <v>1.783</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -696,19 +696,19 @@
         <v>2.968</v>
       </c>
       <c r="G5" t="n">
-        <v>9.494999999999999</v>
+        <v>9.609</v>
       </c>
       <c r="H5" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="I5" t="n">
-        <v>219.9</v>
+        <v>223.7</v>
       </c>
       <c r="J5" t="n">
         <v>10.53</v>
       </c>
       <c r="K5" t="n">
-        <v>1.691</v>
+        <v>1.686</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1074,27 +1074,27 @@
         <v>0.799</v>
       </c>
       <c r="G12" t="n">
-        <v>2.134</v>
+        <v>2.107</v>
       </c>
       <c r="H12" t="n">
-        <v>2.99</v>
+        <v>3.03</v>
       </c>
       <c r="I12" t="n">
-        <v>167.2</v>
+        <v>163.7</v>
       </c>
       <c r="J12" t="n">
         <v>12.5</v>
       </c>
       <c r="K12" t="n">
-        <v>1.419</v>
+        <v>1.534</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1115,40 +1115,40 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>70.8</v>
+        <v>24</v>
       </c>
       <c r="E13" t="n">
-        <v>8.699999999999999</v>
+        <v>13.9</v>
       </c>
       <c r="F13" t="n">
-        <v>8.138</v>
+        <v>1.727</v>
       </c>
       <c r="G13" t="n">
-        <v>21.127</v>
+        <v>4.492</v>
       </c>
       <c r="H13" t="n">
-        <v>3.35</v>
+        <v>5.34</v>
       </c>
       <c r="I13" t="n">
-        <v>159.6</v>
+        <v>160.2</v>
       </c>
       <c r="J13" t="n">
-        <v>11.49</v>
+        <v>7.19</v>
       </c>
       <c r="K13" t="n">
-        <v>1.909</v>
+        <v>1.354</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1173,28 +1173,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>37.14</v>
+        <v>70.8</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>8.074</v>
+        <v>8.138</v>
       </c>
       <c r="G14" t="n">
-        <v>20.528</v>
+        <v>21.127</v>
       </c>
       <c r="H14" t="n">
-        <v>1.81</v>
+        <v>3.35</v>
       </c>
       <c r="I14" t="n">
-        <v>154.3</v>
+        <v>159.6</v>
       </c>
       <c r="J14" t="n">
-        <v>21.74</v>
+        <v>11.49</v>
       </c>
       <c r="K14" t="n">
-        <v>1.806</v>
+        <v>1.909</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1223,32 +1223,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>75.59999999999999</v>
+        <v>37.14</v>
       </c>
       <c r="E15" t="n">
-        <v>11.4</v>
+        <v>4.6</v>
       </c>
       <c r="F15" t="n">
-        <v>6.632</v>
+        <v>8.074</v>
       </c>
       <c r="G15" t="n">
-        <v>16.662</v>
+        <v>20.528</v>
       </c>
       <c r="H15" t="n">
-        <v>4.54</v>
+        <v>1.81</v>
       </c>
       <c r="I15" t="n">
-        <v>151.2</v>
+        <v>154.3</v>
       </c>
       <c r="J15" t="n">
-        <v>8.77</v>
+        <v>21.74</v>
       </c>
       <c r="K15" t="n">
-        <v>1.783</v>
+        <v>1.806</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1277,40 +1277,40 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>13.9</v>
+        <v>11.4</v>
       </c>
       <c r="F16" t="n">
-        <v>1.727</v>
+        <v>6.632</v>
       </c>
       <c r="G16" t="n">
-        <v>4.293</v>
+        <v>16.662</v>
       </c>
       <c r="H16" t="n">
-        <v>5.59</v>
+        <v>4.54</v>
       </c>
       <c r="I16" t="n">
-        <v>148.6</v>
+        <v>151.2</v>
       </c>
       <c r="J16" t="n">
-        <v>7.19</v>
+        <v>8.77</v>
       </c>
       <c r="K16" t="n">
-        <v>1.144</v>
+        <v>1.783</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>mid-cycle</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1344,19 +1344,19 @@
         <v>1.536</v>
       </c>
       <c r="G17" t="n">
-        <v>3.675</v>
+        <v>3.774</v>
       </c>
       <c r="H17" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="I17" t="n">
-        <v>139.3</v>
+        <v>145.7</v>
       </c>
       <c r="J17" t="n">
         <v>10.31</v>
       </c>
       <c r="K17" t="n">
-        <v>1.513</v>
+        <v>1.677</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1398,19 +1398,19 @@
         <v>1.643</v>
       </c>
       <c r="G18" t="n">
-        <v>3.892</v>
+        <v>3.874</v>
       </c>
       <c r="H18" t="n">
-        <v>4.43</v>
+        <v>4.45</v>
       </c>
       <c r="I18" t="n">
-        <v>136.9</v>
+        <v>135.8</v>
       </c>
       <c r="J18" t="n">
         <v>9.52</v>
       </c>
       <c r="K18" t="n">
-        <v>1.209</v>
+        <v>1.374</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1668,19 +1668,19 @@
         <v>3.942</v>
       </c>
       <c r="G23" t="n">
-        <v>5.363</v>
+        <v>5.303</v>
       </c>
       <c r="H23" t="n">
-        <v>5.07</v>
+        <v>5.13</v>
       </c>
       <c r="I23" t="n">
-        <v>36</v>
+        <v>34.5</v>
       </c>
       <c r="J23" t="n">
         <v>14.49</v>
       </c>
       <c r="K23" t="n">
-        <v>1.247</v>
+        <v>1.411</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1356,7 +1356,7 @@
         <v>10.31</v>
       </c>
       <c r="K17" t="n">
-        <v>1.677</v>
+        <v>1.678</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1560,19 +1560,19 @@
         <v>0.347</v>
       </c>
       <c r="G21" t="n">
-        <v>0.537</v>
+        <v>0.541</v>
       </c>
       <c r="H21" t="n">
-        <v>5.18</v>
+        <v>5.14</v>
       </c>
       <c r="I21" t="n">
-        <v>54.6</v>
+        <v>55.7</v>
       </c>
       <c r="J21" t="n">
         <v>12.5</v>
       </c>
       <c r="K21" t="n">
-        <v>1.206</v>
+        <v>1.311</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1614,19 +1614,19 @@
         <v>10.261</v>
       </c>
       <c r="G22" t="n">
-        <v>14.044</v>
+        <v>14.083</v>
       </c>
       <c r="H22" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="I22" t="n">
-        <v>36.9</v>
+        <v>37.3</v>
       </c>
       <c r="J22" t="n">
         <v>26.32</v>
       </c>
       <c r="K22" t="n">
-        <v>1.453</v>
+        <v>1.488</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -525,10 +525,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="E2" t="n">
-        <v>17.2</v>
+        <v>19.2</v>
       </c>
       <c r="F2" t="n">
         <v>0.302</v>
@@ -537,13 +537,13 @@
         <v>1.452</v>
       </c>
       <c r="H2" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>380.2</v>
+        <v>380.5</v>
       </c>
       <c r="J2" t="n">
-        <v>5.81</v>
+        <v>5.21</v>
       </c>
       <c r="K2" t="n">
         <v>2.207</v>
@@ -565,7 +565,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -579,28 +579,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5.4</v>
+        <v>13.31</v>
       </c>
       <c r="E3" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="F3" t="n">
-        <v>0.245</v>
+        <v>0.859</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>3.602</v>
       </c>
       <c r="H3" t="n">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="I3" t="n">
-        <v>307.3</v>
+        <v>319.4</v>
       </c>
       <c r="J3" t="n">
-        <v>4.55</v>
+        <v>6.45</v>
       </c>
       <c r="K3" t="n">
-        <v>2.788</v>
+        <v>2.454</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -633,28 +633,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>5.3</v>
       </c>
       <c r="E4" t="n">
-        <v>11.1</v>
+        <v>19</v>
       </c>
       <c r="F4" t="n">
-        <v>1.099</v>
+        <v>0.279</v>
       </c>
       <c r="G4" t="n">
-        <v>3.602</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>3.39</v>
+        <v>5.3</v>
       </c>
       <c r="I4" t="n">
-        <v>227.7</v>
+        <v>258.4</v>
       </c>
       <c r="J4" t="n">
-        <v>9.01</v>
+        <v>5.26</v>
       </c>
       <c r="K4" t="n">
-        <v>2.454</v>
+        <v>2.788</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28.2</v>
+        <v>27.7</v>
       </c>
       <c r="E5" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>2.968</v>
+        <v>2.978</v>
       </c>
       <c r="G5" t="n">
         <v>9.609</v>
       </c>
       <c r="H5" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="I5" t="n">
-        <v>223.7</v>
+        <v>222.6</v>
       </c>
       <c r="J5" t="n">
-        <v>10.53</v>
+        <v>10.75</v>
       </c>
       <c r="K5" t="n">
         <v>1.686</v>
@@ -727,50 +727,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid proxy)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21.9</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>2.489</v>
+        <v>6.867</v>
       </c>
       <c r="G6" t="n">
-        <v>7.934</v>
+        <v>21.722</v>
       </c>
       <c r="H6" t="n">
-        <v>2.76</v>
+        <v>3.79</v>
       </c>
       <c r="I6" t="n">
-        <v>218.8</v>
+        <v>216.3</v>
       </c>
       <c r="J6" t="n">
-        <v>11.36</v>
+        <v>8.33</v>
       </c>
       <c r="K6" t="n">
-        <v>0.774</v>
+        <v>2.111</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>below-mid</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -781,12 +781,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid proxy)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -795,28 +795,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>78</v>
+        <v>17.2</v>
       </c>
       <c r="E7" t="n">
-        <v>11.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>6.842</v>
+        <v>1.849</v>
       </c>
       <c r="G7" t="n">
-        <v>21.722</v>
+        <v>5.514</v>
       </c>
       <c r="H7" t="n">
-        <v>3.59</v>
+        <v>3.12</v>
       </c>
       <c r="I7" t="n">
-        <v>217.5</v>
+        <v>198.1</v>
       </c>
       <c r="J7" t="n">
-        <v>8.77</v>
+        <v>10.75</v>
       </c>
       <c r="K7" t="n">
-        <v>2.111</v>
+        <v>2.788</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>34.5</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>9.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>3.67</v>
+        <v>0.805</v>
       </c>
       <c r="G8" t="n">
-        <v>11.308</v>
+        <v>2.395</v>
       </c>
       <c r="H8" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="I8" t="n">
-        <v>208.1</v>
+        <v>197.6</v>
       </c>
       <c r="J8" t="n">
-        <v>10.64</v>
+        <v>11.49</v>
       </c>
       <c r="K8" t="n">
-        <v>2.573</v>
+        <v>1.665</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -899,40 +899,40 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>lng</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.7</v>
+        <v>21.6</v>
       </c>
       <c r="E9" t="n">
-        <v>9.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.786</v>
+        <v>2.667</v>
       </c>
       <c r="G9" t="n">
-        <v>2.395</v>
+        <v>7.934</v>
       </c>
       <c r="H9" t="n">
-        <v>3.22</v>
+        <v>2.72</v>
       </c>
       <c r="I9" t="n">
-        <v>204.8</v>
+        <v>197.5</v>
       </c>
       <c r="J9" t="n">
-        <v>10.2</v>
+        <v>12.35</v>
       </c>
       <c r="K9" t="n">
-        <v>1.665</v>
+        <v>0.774</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>below-mid</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -957,28 +957,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.4</v>
+        <v>36.8</v>
       </c>
       <c r="E10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="F10" t="n">
-        <v>1.864</v>
+        <v>3.915</v>
       </c>
       <c r="G10" t="n">
-        <v>5.514</v>
+        <v>11.308</v>
       </c>
       <c r="H10" t="n">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="I10" t="n">
-        <v>195.9</v>
+        <v>188.8</v>
       </c>
       <c r="J10" t="n">
-        <v>11.36</v>
+        <v>10.64</v>
       </c>
       <c r="K10" t="n">
-        <v>2.788</v>
+        <v>2.573</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1011,25 +1011,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>47.7</v>
+        <v>53.1</v>
       </c>
       <c r="E11" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="F11" t="n">
-        <v>5.679</v>
+        <v>5.649</v>
       </c>
       <c r="G11" t="n">
         <v>15.298</v>
       </c>
       <c r="H11" t="n">
-        <v>3.12</v>
+        <v>3.47</v>
       </c>
       <c r="I11" t="n">
-        <v>169.4</v>
+        <v>170.8</v>
       </c>
       <c r="J11" t="n">
-        <v>11.9</v>
+        <v>10.64</v>
       </c>
       <c r="K11" t="n">
         <v>2.511</v>
@@ -1105,7 +1105,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1115,40 +1115,40 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>24</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>13.9</v>
+        <v>8.4</v>
       </c>
       <c r="F13" t="n">
-        <v>1.727</v>
+        <v>8.048</v>
       </c>
       <c r="G13" t="n">
-        <v>4.492</v>
+        <v>21.127</v>
       </c>
       <c r="H13" t="n">
-        <v>5.34</v>
+        <v>3.2</v>
       </c>
       <c r="I13" t="n">
-        <v>160.2</v>
+        <v>162.5</v>
       </c>
       <c r="J13" t="n">
-        <v>7.19</v>
+        <v>11.9</v>
       </c>
       <c r="K13" t="n">
-        <v>1.354</v>
+        <v>1.909</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1169,40 +1169,40 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>70.8</v>
+        <v>24.5</v>
       </c>
       <c r="E14" t="n">
-        <v>8.699999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="F14" t="n">
-        <v>8.138</v>
+        <v>1.725</v>
       </c>
       <c r="G14" t="n">
-        <v>21.127</v>
+        <v>4.492</v>
       </c>
       <c r="H14" t="n">
-        <v>3.35</v>
+        <v>5.45</v>
       </c>
       <c r="I14" t="n">
-        <v>159.6</v>
+        <v>160.4</v>
       </c>
       <c r="J14" t="n">
-        <v>11.49</v>
+        <v>7.04</v>
       </c>
       <c r="K14" t="n">
-        <v>1.909</v>
+        <v>1.354</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1281,25 +1281,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>75.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="E16" t="n">
-        <v>11.4</v>
+        <v>11.1</v>
       </c>
       <c r="F16" t="n">
-        <v>6.632</v>
+        <v>6.577</v>
       </c>
       <c r="G16" t="n">
         <v>16.662</v>
       </c>
       <c r="H16" t="n">
-        <v>4.54</v>
+        <v>4.38</v>
       </c>
       <c r="I16" t="n">
-        <v>151.2</v>
+        <v>153.3</v>
       </c>
       <c r="J16" t="n">
-        <v>8.77</v>
+        <v>9.01</v>
       </c>
       <c r="K16" t="n">
         <v>1.783</v>
@@ -1321,7 +1321,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1331,40 +1331,40 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.9</v>
+        <v>17.25</v>
       </c>
       <c r="E17" t="n">
-        <v>9.699999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="F17" t="n">
-        <v>1.536</v>
+        <v>1.643</v>
       </c>
       <c r="G17" t="n">
-        <v>3.774</v>
+        <v>3.874</v>
       </c>
       <c r="H17" t="n">
-        <v>3.95</v>
+        <v>4.45</v>
       </c>
       <c r="I17" t="n">
-        <v>145.7</v>
+        <v>135.8</v>
       </c>
       <c r="J17" t="n">
-        <v>10.31</v>
+        <v>9.52</v>
       </c>
       <c r="K17" t="n">
-        <v>1.678</v>
+        <v>1.374</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1385,40 +1385,40 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17.25</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="n">
-        <v>10.5</v>
+        <v>8.9</v>
       </c>
       <c r="F18" t="n">
-        <v>1.643</v>
+        <v>1.64</v>
       </c>
       <c r="G18" t="n">
-        <v>3.874</v>
+        <v>3.774</v>
       </c>
       <c r="H18" t="n">
-        <v>4.45</v>
+        <v>3.87</v>
       </c>
       <c r="I18" t="n">
-        <v>135.8</v>
+        <v>130</v>
       </c>
       <c r="J18" t="n">
-        <v>9.52</v>
+        <v>11.24</v>
       </c>
       <c r="K18" t="n">
-        <v>1.374</v>
+        <v>1.678</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1443,25 +1443,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>14.9</v>
       </c>
       <c r="E19" t="n">
-        <v>14.2</v>
+        <v>13.2</v>
       </c>
       <c r="F19" t="n">
-        <v>1.127</v>
+        <v>1.129</v>
       </c>
       <c r="G19" t="n">
         <v>2.221</v>
       </c>
       <c r="H19" t="n">
-        <v>7.2</v>
+        <v>6.71</v>
       </c>
       <c r="I19" t="n">
-        <v>97.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="J19" t="n">
-        <v>7.04</v>
+        <v>7.58</v>
       </c>
       <c r="K19" t="n">
         <v>1.375</v>
@@ -1497,25 +1497,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.7</v>
+        <v>29.3</v>
       </c>
       <c r="E20" t="n">
-        <v>14.5</v>
+        <v>14.1</v>
       </c>
       <c r="F20" t="n">
-        <v>2.048</v>
+        <v>2.078</v>
       </c>
       <c r="G20" t="n">
         <v>3.74</v>
       </c>
       <c r="H20" t="n">
-        <v>7.94</v>
+        <v>7.83</v>
       </c>
       <c r="I20" t="n">
-        <v>82.59999999999999</v>
+        <v>80</v>
       </c>
       <c r="J20" t="n">
-        <v>6.9</v>
+        <v>7.09</v>
       </c>
       <c r="K20" t="n">
         <v>0.706</v>
@@ -1551,25 +1551,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2.78</v>
+        <v>2.44</v>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="F21" t="n">
-        <v>0.347</v>
+        <v>0.317</v>
       </c>
       <c r="G21" t="n">
         <v>0.541</v>
       </c>
       <c r="H21" t="n">
-        <v>5.14</v>
+        <v>4.51</v>
       </c>
       <c r="I21" t="n">
-        <v>55.7</v>
+        <v>70.7</v>
       </c>
       <c r="J21" t="n">
-        <v>12.5</v>
+        <v>12.99</v>
       </c>
       <c r="K21" t="n">
         <v>1.311</v>
@@ -1659,25 +1659,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>27.2</v>
+        <v>25.2</v>
       </c>
       <c r="E23" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="F23" t="n">
-        <v>3.942</v>
+        <v>3.937</v>
       </c>
       <c r="G23" t="n">
         <v>5.303</v>
       </c>
       <c r="H23" t="n">
-        <v>5.13</v>
+        <v>4.75</v>
       </c>
       <c r="I23" t="n">
-        <v>34.5</v>
+        <v>34.7</v>
       </c>
       <c r="J23" t="n">
-        <v>14.49</v>
+        <v>15.62</v>
       </c>
       <c r="K23" t="n">
         <v>1.411</v>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1537,7 +1537,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>BWLP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1547,40 +1547,40 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>containerships</t>
+          <t>lpg</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2.44</v>
+        <v>18.52</v>
       </c>
       <c r="E21" t="n">
-        <v>7.7</v>
+        <v>9.9</v>
       </c>
       <c r="F21" t="n">
-        <v>0.317</v>
+        <v>1.871</v>
       </c>
       <c r="G21" t="n">
-        <v>0.541</v>
+        <v>3.229</v>
       </c>
       <c r="H21" t="n">
-        <v>4.51</v>
+        <v>5.74</v>
       </c>
       <c r="I21" t="n">
-        <v>70.7</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>12.99</v>
+        <v>10.1</v>
       </c>
       <c r="K21" t="n">
-        <v>1.311</v>
+        <v>1.59</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1605,28 +1605,28 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>38.99</v>
+        <v>2.44</v>
       </c>
       <c r="E22" t="n">
-        <v>3.8</v>
+        <v>7.7</v>
       </c>
       <c r="F22" t="n">
-        <v>10.261</v>
+        <v>0.317</v>
       </c>
       <c r="G22" t="n">
-        <v>14.083</v>
+        <v>0.541</v>
       </c>
       <c r="H22" t="n">
-        <v>2.77</v>
+        <v>4.51</v>
       </c>
       <c r="I22" t="n">
-        <v>37.3</v>
+        <v>70.7</v>
       </c>
       <c r="J22" t="n">
-        <v>26.32</v>
+        <v>12.99</v>
       </c>
       <c r="K22" t="n">
-        <v>1.488</v>
+        <v>1.311</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1645,52 +1645,160 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>LPG</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>lpg</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>36</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.871</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5.753</v>
+      </c>
+      <c r="H23" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="I23" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>late-cycle/peak</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>earnings-driven (tool&gt;cons)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>containerships</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F24" t="n">
+        <v>10.261</v>
+      </c>
+      <c r="G24" t="n">
+        <v>14.083</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="I24" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.488</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>elevated</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>earnings-driven (tool&gt;cons)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>SBLK</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>whole-company</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>dry_bulk</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D25" t="n">
         <v>25.2</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E25" t="n">
         <v>6.4</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F25" t="n">
         <v>3.937</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G25" t="n">
         <v>5.303</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H25" t="n">
         <v>4.75</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I25" t="n">
         <v>34.7</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J25" t="n">
         <v>15.62</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K25" t="n">
         <v>1.411</v>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>elevated</t>
         </is>
       </c>
-      <c r="M23" t="n">
+      <c r="M25" t="n">
         <v>0.4</v>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>earnings-driven (tool&gt;cons)</t>
         </is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -997,7 +997,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1007,40 +1007,40 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>53.1</v>
+        <v>24.5</v>
       </c>
       <c r="E11" t="n">
-        <v>9.4</v>
+        <v>14.2</v>
       </c>
       <c r="F11" t="n">
-        <v>5.649</v>
+        <v>1.725</v>
       </c>
       <c r="G11" t="n">
-        <v>15.298</v>
+        <v>4.731</v>
       </c>
       <c r="H11" t="n">
-        <v>3.47</v>
+        <v>5.18</v>
       </c>
       <c r="I11" t="n">
-        <v>170.8</v>
+        <v>174.2</v>
       </c>
       <c r="J11" t="n">
-        <v>10.64</v>
+        <v>7.04</v>
       </c>
       <c r="K11" t="n">
-        <v>2.511</v>
+        <v>1.423</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1074,19 +1074,19 @@
         <v>0.799</v>
       </c>
       <c r="G12" t="n">
-        <v>2.107</v>
+        <v>2.186</v>
       </c>
       <c r="H12" t="n">
-        <v>3.03</v>
+        <v>2.92</v>
       </c>
       <c r="I12" t="n">
-        <v>163.7</v>
+        <v>173.7</v>
       </c>
       <c r="J12" t="n">
         <v>12.5</v>
       </c>
       <c r="K12" t="n">
-        <v>1.534</v>
+        <v>1.616</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1119,28 +1119,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>67.59999999999999</v>
+        <v>53.1</v>
       </c>
       <c r="E13" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="F13" t="n">
-        <v>8.048</v>
+        <v>5.649</v>
       </c>
       <c r="G13" t="n">
-        <v>21.127</v>
+        <v>15.298</v>
       </c>
       <c r="H13" t="n">
-        <v>3.2</v>
+        <v>3.47</v>
       </c>
       <c r="I13" t="n">
-        <v>162.5</v>
+        <v>170.8</v>
       </c>
       <c r="J13" t="n">
-        <v>11.9</v>
+        <v>10.64</v>
       </c>
       <c r="K13" t="n">
-        <v>1.909</v>
+        <v>2.511</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1169,40 +1169,40 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>24.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>14.2</v>
+        <v>8.4</v>
       </c>
       <c r="F14" t="n">
-        <v>1.725</v>
+        <v>8.048</v>
       </c>
       <c r="G14" t="n">
-        <v>4.492</v>
+        <v>21.127</v>
       </c>
       <c r="H14" t="n">
-        <v>5.45</v>
+        <v>3.2</v>
       </c>
       <c r="I14" t="n">
-        <v>160.4</v>
+        <v>162.5</v>
       </c>
       <c r="J14" t="n">
-        <v>7.04</v>
+        <v>11.9</v>
       </c>
       <c r="K14" t="n">
-        <v>1.354</v>
+        <v>1.909</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1344,19 +1344,19 @@
         <v>1.643</v>
       </c>
       <c r="G17" t="n">
-        <v>3.874</v>
+        <v>4.154</v>
       </c>
       <c r="H17" t="n">
-        <v>4.45</v>
+        <v>4.15</v>
       </c>
       <c r="I17" t="n">
-        <v>135.8</v>
+        <v>152.9</v>
       </c>
       <c r="J17" t="n">
         <v>9.52</v>
       </c>
       <c r="K17" t="n">
-        <v>1.374</v>
+        <v>1.434</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1398,19 +1398,19 @@
         <v>1.64</v>
       </c>
       <c r="G18" t="n">
-        <v>3.774</v>
+        <v>3.927</v>
       </c>
       <c r="H18" t="n">
-        <v>3.87</v>
+        <v>3.72</v>
       </c>
       <c r="I18" t="n">
-        <v>130</v>
+        <v>139.4</v>
       </c>
       <c r="J18" t="n">
         <v>11.24</v>
       </c>
       <c r="K18" t="n">
-        <v>1.678</v>
+        <v>1.742</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1709,32 +1709,32 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>containerships</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>38.99</v>
+        <v>25.2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="F24" t="n">
-        <v>10.261</v>
+        <v>3.937</v>
       </c>
       <c r="G24" t="n">
-        <v>14.083</v>
+        <v>5.614</v>
       </c>
       <c r="H24" t="n">
-        <v>2.77</v>
+        <v>4.49</v>
       </c>
       <c r="I24" t="n">
-        <v>37.3</v>
+        <v>42.6</v>
       </c>
       <c r="J24" t="n">
-        <v>26.32</v>
+        <v>15.62</v>
       </c>
       <c r="K24" t="n">
-        <v>1.488</v>
+        <v>1.479</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1763,32 +1763,32 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>containerships</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25.2</v>
+        <v>38.99</v>
       </c>
       <c r="E25" t="n">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="F25" t="n">
-        <v>3.937</v>
+        <v>10.261</v>
       </c>
       <c r="G25" t="n">
-        <v>5.303</v>
+        <v>14.083</v>
       </c>
       <c r="H25" t="n">
-        <v>4.75</v>
+        <v>2.77</v>
       </c>
       <c r="I25" t="n">
-        <v>34.7</v>
+        <v>37.3</v>
       </c>
       <c r="J25" t="n">
-        <v>15.62</v>
+        <v>26.32</v>
       </c>
       <c r="K25" t="n">
-        <v>1.411</v>
+        <v>1.488</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1429,7 +1429,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1439,32 +1439,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.9</v>
+        <v>0.39</v>
       </c>
       <c r="E19" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="F19" t="n">
-        <v>1.129</v>
+        <v>0.03</v>
       </c>
       <c r="G19" t="n">
-        <v>2.221</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>6.71</v>
+        <v>5.67</v>
       </c>
       <c r="I19" t="n">
-        <v>96.8</v>
+        <v>129.2</v>
       </c>
       <c r="J19" t="n">
-        <v>7.58</v>
+        <v>7.69</v>
       </c>
       <c r="K19" t="n">
-        <v>1.375</v>
+        <v>1.226</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1493,40 +1493,40 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.3</v>
+        <v>14.9</v>
       </c>
       <c r="E20" t="n">
-        <v>14.1</v>
+        <v>13.2</v>
       </c>
       <c r="F20" t="n">
-        <v>2.078</v>
+        <v>1.129</v>
       </c>
       <c r="G20" t="n">
-        <v>3.74</v>
+        <v>2.221</v>
       </c>
       <c r="H20" t="n">
-        <v>7.83</v>
+        <v>6.71</v>
       </c>
       <c r="I20" t="n">
-        <v>80</v>
+        <v>96.8</v>
       </c>
       <c r="J20" t="n">
-        <v>7.09</v>
+        <v>7.58</v>
       </c>
       <c r="K20" t="n">
-        <v>0.706</v>
+        <v>1.375</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>below-mid</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BWLP</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1547,40 +1547,40 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>lpg</t>
+          <t>lng</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>18.52</v>
+        <v>29.3</v>
       </c>
       <c r="E21" t="n">
-        <v>9.9</v>
+        <v>14.1</v>
       </c>
       <c r="F21" t="n">
-        <v>1.871</v>
+        <v>2.078</v>
       </c>
       <c r="G21" t="n">
-        <v>3.229</v>
+        <v>3.74</v>
       </c>
       <c r="H21" t="n">
-        <v>5.74</v>
+        <v>7.83</v>
       </c>
       <c r="I21" t="n">
-        <v>72.59999999999999</v>
+        <v>80</v>
       </c>
       <c r="J21" t="n">
-        <v>10.1</v>
+        <v>7.09</v>
       </c>
       <c r="K21" t="n">
-        <v>1.59</v>
+        <v>0.706</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>below-mid</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>BWLP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1601,40 +1601,40 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>containerships</t>
+          <t>lpg</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.44</v>
+        <v>18.52</v>
       </c>
       <c r="E22" t="n">
-        <v>7.7</v>
+        <v>9.9</v>
       </c>
       <c r="F22" t="n">
-        <v>0.317</v>
+        <v>1.871</v>
       </c>
       <c r="G22" t="n">
-        <v>0.541</v>
+        <v>3.229</v>
       </c>
       <c r="H22" t="n">
-        <v>4.51</v>
+        <v>5.74</v>
       </c>
       <c r="I22" t="n">
-        <v>70.7</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>12.99</v>
+        <v>10.1</v>
       </c>
       <c r="K22" t="n">
-        <v>1.311</v>
+        <v>1.59</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1655,40 +1655,40 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>lpg</t>
+          <t>containerships</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>36</v>
+        <v>2.44</v>
       </c>
       <c r="E23" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="F23" t="n">
-        <v>3.871</v>
+        <v>0.317</v>
       </c>
       <c r="G23" t="n">
-        <v>5.753</v>
+        <v>0.541</v>
       </c>
       <c r="H23" t="n">
-        <v>6.26</v>
+        <v>4.51</v>
       </c>
       <c r="I23" t="n">
-        <v>48.6</v>
+        <v>70.7</v>
       </c>
       <c r="J23" t="n">
-        <v>10.75</v>
+        <v>12.99</v>
       </c>
       <c r="K23" t="n">
-        <v>1.59</v>
+        <v>1.311</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1709,40 +1709,40 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>lpg</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>25.2</v>
+        <v>36</v>
       </c>
       <c r="E24" t="n">
-        <v>6.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>3.937</v>
+        <v>3.871</v>
       </c>
       <c r="G24" t="n">
-        <v>5.614</v>
+        <v>5.753</v>
       </c>
       <c r="H24" t="n">
-        <v>4.49</v>
+        <v>6.26</v>
       </c>
       <c r="I24" t="n">
-        <v>42.6</v>
+        <v>48.6</v>
       </c>
       <c r="J24" t="n">
-        <v>15.62</v>
+        <v>10.75</v>
       </c>
       <c r="K24" t="n">
-        <v>1.479</v>
+        <v>1.59</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1763,32 +1763,32 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>containerships</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>38.99</v>
+        <v>25.2</v>
       </c>
       <c r="E25" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="F25" t="n">
-        <v>10.261</v>
+        <v>3.937</v>
       </c>
       <c r="G25" t="n">
-        <v>14.083</v>
+        <v>5.614</v>
       </c>
       <c r="H25" t="n">
-        <v>2.77</v>
+        <v>4.49</v>
       </c>
       <c r="I25" t="n">
-        <v>37.3</v>
+        <v>42.6</v>
       </c>
       <c r="J25" t="n">
-        <v>26.32</v>
+        <v>15.62</v>
       </c>
       <c r="K25" t="n">
-        <v>1.488</v>
+        <v>1.479</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1799,6 +1799,60 @@
         <v>0.4</v>
       </c>
       <c r="N25" t="inlineStr">
+        <is>
+          <t>earnings-driven (tool&gt;cons)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>containerships</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F26" t="n">
+        <v>10.261</v>
+      </c>
+      <c r="G26" t="n">
+        <v>14.083</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="I26" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.488</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>elevated</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>earnings-driven (tool&gt;cons)</t>
         </is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1213,7 +1213,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1223,32 +1223,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>37.14</v>
+        <v>73</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6</v>
+        <v>11.1</v>
       </c>
       <c r="F15" t="n">
-        <v>8.074</v>
+        <v>6.577</v>
       </c>
       <c r="G15" t="n">
-        <v>20.528</v>
+        <v>16.662</v>
       </c>
       <c r="H15" t="n">
-        <v>1.81</v>
+        <v>4.38</v>
       </c>
       <c r="I15" t="n">
-        <v>154.3</v>
+        <v>153.3</v>
       </c>
       <c r="J15" t="n">
-        <v>21.74</v>
+        <v>9.01</v>
       </c>
       <c r="K15" t="n">
-        <v>1.806</v>
+        <v>1.783</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1277,40 +1277,40 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>73</v>
+        <v>17.25</v>
       </c>
       <c r="E16" t="n">
-        <v>11.1</v>
+        <v>10.5</v>
       </c>
       <c r="F16" t="n">
-        <v>6.577</v>
+        <v>1.643</v>
       </c>
       <c r="G16" t="n">
-        <v>16.662</v>
+        <v>4.154</v>
       </c>
       <c r="H16" t="n">
-        <v>4.38</v>
+        <v>4.15</v>
       </c>
       <c r="I16" t="n">
-        <v>153.3</v>
+        <v>152.9</v>
       </c>
       <c r="J16" t="n">
-        <v>9.01</v>
+        <v>9.52</v>
       </c>
       <c r="K16" t="n">
-        <v>1.783</v>
+        <v>1.434</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1331,40 +1331,40 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17.25</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="n">
-        <v>10.5</v>
+        <v>8.9</v>
       </c>
       <c r="F17" t="n">
-        <v>1.643</v>
+        <v>1.64</v>
       </c>
       <c r="G17" t="n">
-        <v>4.154</v>
+        <v>3.927</v>
       </c>
       <c r="H17" t="n">
-        <v>4.15</v>
+        <v>3.72</v>
       </c>
       <c r="I17" t="n">
-        <v>152.9</v>
+        <v>139.4</v>
       </c>
       <c r="J17" t="n">
-        <v>9.52</v>
+        <v>11.24</v>
       </c>
       <c r="K17" t="n">
-        <v>1.434</v>
+        <v>1.742</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1385,40 +1385,40 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>0.39</v>
       </c>
       <c r="E18" t="n">
-        <v>8.9</v>
+        <v>13</v>
       </c>
       <c r="F18" t="n">
-        <v>1.64</v>
+        <v>0.03</v>
       </c>
       <c r="G18" t="n">
-        <v>3.927</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>3.72</v>
+        <v>5.67</v>
       </c>
       <c r="I18" t="n">
-        <v>139.4</v>
+        <v>129.2</v>
       </c>
       <c r="J18" t="n">
-        <v>11.24</v>
+        <v>7.69</v>
       </c>
       <c r="K18" t="n">
-        <v>1.742</v>
+        <v>1.226</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1439,40 +1439,40 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.39</v>
+        <v>37.14</v>
       </c>
       <c r="E19" t="n">
-        <v>13</v>
+        <v>4.6</v>
       </c>
       <c r="F19" t="n">
-        <v>0.03</v>
+        <v>8.074</v>
       </c>
       <c r="G19" t="n">
-        <v>0.06900000000000001</v>
+        <v>17.681</v>
       </c>
       <c r="H19" t="n">
-        <v>5.67</v>
+        <v>2.1</v>
       </c>
       <c r="I19" t="n">
-        <v>129.2</v>
+        <v>119</v>
       </c>
       <c r="J19" t="n">
-        <v>7.69</v>
+        <v>21.74</v>
       </c>
       <c r="K19" t="n">
-        <v>1.226</v>
+        <v>1.771</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1674,13 +1674,13 @@
         <v>4.51</v>
       </c>
       <c r="I23" t="n">
-        <v>70.7</v>
+        <v>70.8</v>
       </c>
       <c r="J23" t="n">
         <v>12.99</v>
       </c>
       <c r="K23" t="n">
-        <v>1.311</v>
+        <v>1.317</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1020,19 +1020,19 @@
         <v>1.725</v>
       </c>
       <c r="G11" t="n">
-        <v>4.731</v>
+        <v>4.794</v>
       </c>
       <c r="H11" t="n">
-        <v>5.18</v>
+        <v>5.11</v>
       </c>
       <c r="I11" t="n">
-        <v>174.2</v>
+        <v>177.9</v>
       </c>
       <c r="J11" t="n">
         <v>7.04</v>
       </c>
       <c r="K11" t="n">
-        <v>1.423</v>
+        <v>1.435</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1074,19 +1074,19 @@
         <v>0.799</v>
       </c>
       <c r="G12" t="n">
-        <v>2.186</v>
+        <v>2.19</v>
       </c>
       <c r="H12" t="n">
         <v>2.92</v>
       </c>
       <c r="I12" t="n">
-        <v>173.7</v>
+        <v>174.1</v>
       </c>
       <c r="J12" t="n">
         <v>12.5</v>
       </c>
       <c r="K12" t="n">
-        <v>1.616</v>
+        <v>1.591</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1223,40 +1223,40 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>73</v>
+        <v>17.25</v>
       </c>
       <c r="E15" t="n">
-        <v>11.1</v>
+        <v>10.5</v>
       </c>
       <c r="F15" t="n">
-        <v>6.577</v>
+        <v>1.643</v>
       </c>
       <c r="G15" t="n">
-        <v>16.662</v>
+        <v>4.225</v>
       </c>
       <c r="H15" t="n">
-        <v>4.38</v>
+        <v>4.08</v>
       </c>
       <c r="I15" t="n">
-        <v>153.3</v>
+        <v>157.2</v>
       </c>
       <c r="J15" t="n">
-        <v>9.01</v>
+        <v>9.52</v>
       </c>
       <c r="K15" t="n">
-        <v>1.783</v>
+        <v>1.445</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1277,40 +1277,40 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17.25</v>
+        <v>73</v>
       </c>
       <c r="E16" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="F16" t="n">
-        <v>1.643</v>
+        <v>6.577</v>
       </c>
       <c r="G16" t="n">
-        <v>4.154</v>
+        <v>16.662</v>
       </c>
       <c r="H16" t="n">
-        <v>4.15</v>
+        <v>4.38</v>
       </c>
       <c r="I16" t="n">
-        <v>152.9</v>
+        <v>153.3</v>
       </c>
       <c r="J16" t="n">
-        <v>9.52</v>
+        <v>9.01</v>
       </c>
       <c r="K16" t="n">
-        <v>1.434</v>
+        <v>1.783</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1344,19 +1344,19 @@
         <v>1.64</v>
       </c>
       <c r="G17" t="n">
-        <v>3.927</v>
+        <v>3.952</v>
       </c>
       <c r="H17" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="I17" t="n">
-        <v>139.4</v>
+        <v>140.9</v>
       </c>
       <c r="J17" t="n">
         <v>11.24</v>
       </c>
       <c r="K17" t="n">
-        <v>1.742</v>
+        <v>1.739</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1398,19 +1398,19 @@
         <v>0.03</v>
       </c>
       <c r="G18" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>5.67</v>
+        <v>5.54</v>
       </c>
       <c r="I18" t="n">
-        <v>129.2</v>
+        <v>134.7</v>
       </c>
       <c r="J18" t="n">
         <v>7.69</v>
       </c>
       <c r="K18" t="n">
-        <v>1.226</v>
+        <v>1.242</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1776,19 +1776,19 @@
         <v>3.937</v>
       </c>
       <c r="G25" t="n">
-        <v>5.614</v>
+        <v>5.67</v>
       </c>
       <c r="H25" t="n">
-        <v>4.49</v>
+        <v>4.44</v>
       </c>
       <c r="I25" t="n">
-        <v>42.6</v>
+        <v>44</v>
       </c>
       <c r="J25" t="n">
         <v>15.62</v>
       </c>
       <c r="K25" t="n">
-        <v>1.479</v>
+        <v>1.481</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1051,7 +1051,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1061,32 +1061,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.39</v>
+        <v>53.1</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="F12" t="n">
-        <v>0.799</v>
+        <v>5.649</v>
       </c>
       <c r="G12" t="n">
-        <v>2.19</v>
+        <v>15.298</v>
       </c>
       <c r="H12" t="n">
-        <v>2.92</v>
+        <v>3.47</v>
       </c>
       <c r="I12" t="n">
-        <v>174.1</v>
+        <v>170.8</v>
       </c>
       <c r="J12" t="n">
-        <v>12.5</v>
+        <v>10.64</v>
       </c>
       <c r="K12" t="n">
-        <v>1.591</v>
+        <v>2.511</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1119,28 +1119,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>53.1</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="F13" t="n">
-        <v>5.649</v>
+        <v>8.048</v>
       </c>
       <c r="G13" t="n">
-        <v>15.298</v>
+        <v>21.127</v>
       </c>
       <c r="H13" t="n">
-        <v>3.47</v>
+        <v>3.2</v>
       </c>
       <c r="I13" t="n">
-        <v>170.8</v>
+        <v>162.5</v>
       </c>
       <c r="J13" t="n">
-        <v>10.64</v>
+        <v>11.9</v>
       </c>
       <c r="K13" t="n">
-        <v>2.511</v>
+        <v>1.909</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1169,40 +1169,40 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>67.59999999999999</v>
+        <v>17.25</v>
       </c>
       <c r="E14" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="F14" t="n">
-        <v>8.048</v>
+        <v>1.643</v>
       </c>
       <c r="G14" t="n">
-        <v>21.127</v>
+        <v>4.225</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2</v>
+        <v>4.08</v>
       </c>
       <c r="I14" t="n">
-        <v>162.5</v>
+        <v>157.2</v>
       </c>
       <c r="J14" t="n">
-        <v>11.9</v>
+        <v>9.52</v>
       </c>
       <c r="K14" t="n">
-        <v>1.909</v>
+        <v>1.445</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1227,36 +1227,36 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17.25</v>
+        <v>6.39</v>
       </c>
       <c r="E15" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="F15" t="n">
-        <v>1.643</v>
+        <v>0.799</v>
       </c>
       <c r="G15" t="n">
-        <v>4.225</v>
+        <v>2.047</v>
       </c>
       <c r="H15" t="n">
-        <v>4.08</v>
+        <v>3.12</v>
       </c>
       <c r="I15" t="n">
-        <v>157.2</v>
+        <v>156.3</v>
       </c>
       <c r="J15" t="n">
-        <v>9.52</v>
+        <v>12.5</v>
       </c>
       <c r="K15" t="n">
-        <v>1.445</v>
+        <v>1.592</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1128,19 +1128,19 @@
         <v>8.048</v>
       </c>
       <c r="G13" t="n">
-        <v>21.127</v>
+        <v>21.357</v>
       </c>
       <c r="H13" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="I13" t="n">
-        <v>162.5</v>
+        <v>165.4</v>
       </c>
       <c r="J13" t="n">
         <v>11.9</v>
       </c>
       <c r="K13" t="n">
-        <v>1.909</v>
+        <v>1.903</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1051,7 +1051,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1061,32 +1061,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>53.1</v>
+        <v>6.39</v>
       </c>
       <c r="E12" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
-        <v>5.649</v>
+        <v>0.799</v>
       </c>
       <c r="G12" t="n">
-        <v>15.298</v>
+        <v>2.19</v>
       </c>
       <c r="H12" t="n">
-        <v>3.47</v>
+        <v>2.92</v>
       </c>
       <c r="I12" t="n">
-        <v>170.8</v>
+        <v>174.1</v>
       </c>
       <c r="J12" t="n">
-        <v>10.64</v>
+        <v>12.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.511</v>
+        <v>1.591</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1119,28 +1119,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>67.59999999999999</v>
+        <v>53.1</v>
       </c>
       <c r="E13" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="F13" t="n">
-        <v>8.048</v>
+        <v>5.649</v>
       </c>
       <c r="G13" t="n">
-        <v>21.357</v>
+        <v>15.298</v>
       </c>
       <c r="H13" t="n">
-        <v>3.17</v>
+        <v>3.47</v>
       </c>
       <c r="I13" t="n">
-        <v>165.4</v>
+        <v>170.8</v>
       </c>
       <c r="J13" t="n">
-        <v>11.9</v>
+        <v>10.64</v>
       </c>
       <c r="K13" t="n">
-        <v>1.903</v>
+        <v>2.511</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1169,40 +1169,40 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.25</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="F14" t="n">
-        <v>1.643</v>
+        <v>8.048</v>
       </c>
       <c r="G14" t="n">
-        <v>4.225</v>
+        <v>21.127</v>
       </c>
       <c r="H14" t="n">
-        <v>4.08</v>
+        <v>3.2</v>
       </c>
       <c r="I14" t="n">
-        <v>157.2</v>
+        <v>162.5</v>
       </c>
       <c r="J14" t="n">
-        <v>9.52</v>
+        <v>11.9</v>
       </c>
       <c r="K14" t="n">
-        <v>1.445</v>
+        <v>1.909</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1227,36 +1227,36 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6.39</v>
+        <v>17.25</v>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="F15" t="n">
-        <v>0.799</v>
+        <v>1.643</v>
       </c>
       <c r="G15" t="n">
-        <v>2.047</v>
+        <v>4.225</v>
       </c>
       <c r="H15" t="n">
-        <v>3.12</v>
+        <v>4.08</v>
       </c>
       <c r="I15" t="n">
-        <v>156.3</v>
+        <v>157.2</v>
       </c>
       <c r="J15" t="n">
-        <v>12.5</v>
+        <v>9.52</v>
       </c>
       <c r="K15" t="n">
-        <v>1.592</v>
+        <v>1.445</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1051,7 +1051,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1061,40 +1061,40 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.39</v>
+        <v>14.9</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>13.2</v>
       </c>
       <c r="F12" t="n">
-        <v>0.799</v>
+        <v>1.129</v>
       </c>
       <c r="G12" t="n">
-        <v>2.19</v>
+        <v>3.086</v>
       </c>
       <c r="H12" t="n">
-        <v>2.92</v>
+        <v>4.83</v>
       </c>
       <c r="I12" t="n">
-        <v>174.1</v>
+        <v>173.4</v>
       </c>
       <c r="J12" t="n">
-        <v>12.5</v>
+        <v>7.58</v>
       </c>
       <c r="K12" t="n">
-        <v>1.591</v>
+        <v>1.375</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1182,19 +1182,19 @@
         <v>8.048</v>
       </c>
       <c r="G14" t="n">
-        <v>21.127</v>
+        <v>21.335</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="I14" t="n">
-        <v>162.5</v>
+        <v>165.1</v>
       </c>
       <c r="J14" t="n">
         <v>11.9</v>
       </c>
       <c r="K14" t="n">
-        <v>1.909</v>
+        <v>1.903</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1277,32 +1277,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>73</v>
+        <v>6.39</v>
       </c>
       <c r="E16" t="n">
-        <v>11.1</v>
+        <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>6.577</v>
+        <v>0.799</v>
       </c>
       <c r="G16" t="n">
-        <v>16.662</v>
+        <v>2.047</v>
       </c>
       <c r="H16" t="n">
-        <v>4.38</v>
+        <v>3.12</v>
       </c>
       <c r="I16" t="n">
-        <v>153.3</v>
+        <v>156.2</v>
       </c>
       <c r="J16" t="n">
-        <v>9.01</v>
+        <v>12.5</v>
       </c>
       <c r="K16" t="n">
-        <v>1.783</v>
+        <v>1.592</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>73</v>
       </c>
       <c r="E17" t="n">
-        <v>8.9</v>
+        <v>11.1</v>
       </c>
       <c r="F17" t="n">
-        <v>1.64</v>
+        <v>6.577</v>
       </c>
       <c r="G17" t="n">
-        <v>3.952</v>
+        <v>16.662</v>
       </c>
       <c r="H17" t="n">
-        <v>3.69</v>
+        <v>4.38</v>
       </c>
       <c r="I17" t="n">
-        <v>140.9</v>
+        <v>153.3</v>
       </c>
       <c r="J17" t="n">
-        <v>11.24</v>
+        <v>9.01</v>
       </c>
       <c r="K17" t="n">
-        <v>1.739</v>
+        <v>1.783</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1385,40 +1385,40 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.39</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="n">
-        <v>13</v>
+        <v>8.9</v>
       </c>
       <c r="F18" t="n">
-        <v>0.03</v>
+        <v>1.64</v>
       </c>
       <c r="G18" t="n">
-        <v>0.07000000000000001</v>
+        <v>3.952</v>
       </c>
       <c r="H18" t="n">
-        <v>5.54</v>
+        <v>3.69</v>
       </c>
       <c r="I18" t="n">
-        <v>134.7</v>
+        <v>140.9</v>
       </c>
       <c r="J18" t="n">
-        <v>7.69</v>
+        <v>11.24</v>
       </c>
       <c r="K18" t="n">
-        <v>1.242</v>
+        <v>1.739</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1439,40 +1439,40 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>37.14</v>
+        <v>0.39</v>
       </c>
       <c r="E19" t="n">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="F19" t="n">
-        <v>8.074</v>
+        <v>0.03</v>
       </c>
       <c r="G19" t="n">
-        <v>17.681</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1</v>
+        <v>5.54</v>
       </c>
       <c r="I19" t="n">
-        <v>119</v>
+        <v>134.7</v>
       </c>
       <c r="J19" t="n">
-        <v>21.74</v>
+        <v>7.69</v>
       </c>
       <c r="K19" t="n">
-        <v>1.771</v>
+        <v>1.242</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1493,40 +1493,40 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.9</v>
+        <v>37.14</v>
       </c>
       <c r="E20" t="n">
-        <v>13.2</v>
+        <v>4.6</v>
       </c>
       <c r="F20" t="n">
-        <v>1.129</v>
+        <v>8.074</v>
       </c>
       <c r="G20" t="n">
-        <v>2.221</v>
+        <v>17.681</v>
       </c>
       <c r="H20" t="n">
-        <v>6.71</v>
+        <v>2.1</v>
       </c>
       <c r="I20" t="n">
-        <v>96.8</v>
+        <v>119</v>
       </c>
       <c r="J20" t="n">
-        <v>7.58</v>
+        <v>21.74</v>
       </c>
       <c r="K20" t="n">
-        <v>1.375</v>
+        <v>1.771</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1140,7 +1140,7 @@
         <v>10.64</v>
       </c>
       <c r="K13" t="n">
-        <v>2.511</v>
+        <v>2.51</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -835,7 +835,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -845,40 +845,40 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>lng</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>21.6</v>
       </c>
       <c r="E8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.805</v>
+        <v>2.667</v>
       </c>
       <c r="G8" t="n">
-        <v>2.395</v>
+        <v>7.948</v>
       </c>
       <c r="H8" t="n">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="I8" t="n">
-        <v>197.6</v>
+        <v>198</v>
       </c>
       <c r="J8" t="n">
-        <v>11.49</v>
+        <v>12.35</v>
       </c>
       <c r="K8" t="n">
-        <v>1.665</v>
+        <v>0.781</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>below-mid</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -899,40 +899,40 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21.6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>8.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>2.667</v>
+        <v>0.805</v>
       </c>
       <c r="G9" t="n">
-        <v>7.934</v>
+        <v>2.395</v>
       </c>
       <c r="H9" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="I9" t="n">
-        <v>197.5</v>
+        <v>197.6</v>
       </c>
       <c r="J9" t="n">
-        <v>12.35</v>
+        <v>11.49</v>
       </c>
       <c r="K9" t="n">
-        <v>0.774</v>
+        <v>1.665</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>below-mid</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1321,7 +1321,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>73</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="n">
-        <v>11.1</v>
+        <v>8.9</v>
       </c>
       <c r="F17" t="n">
-        <v>6.577</v>
+        <v>1.64</v>
       </c>
       <c r="G17" t="n">
-        <v>16.662</v>
+        <v>3.952</v>
       </c>
       <c r="H17" t="n">
-        <v>4.38</v>
+        <v>3.69</v>
       </c>
       <c r="I17" t="n">
-        <v>153.3</v>
+        <v>140.9</v>
       </c>
       <c r="J17" t="n">
-        <v>9.01</v>
+        <v>11.24</v>
       </c>
       <c r="K17" t="n">
-        <v>1.783</v>
+        <v>1.739</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1385,40 +1385,40 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>0.39</v>
       </c>
       <c r="E18" t="n">
-        <v>8.9</v>
+        <v>13</v>
       </c>
       <c r="F18" t="n">
-        <v>1.64</v>
+        <v>0.03</v>
       </c>
       <c r="G18" t="n">
-        <v>3.952</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>3.69</v>
+        <v>5.54</v>
       </c>
       <c r="I18" t="n">
-        <v>140.9</v>
+        <v>134.7</v>
       </c>
       <c r="J18" t="n">
-        <v>11.24</v>
+        <v>7.69</v>
       </c>
       <c r="K18" t="n">
-        <v>1.739</v>
+        <v>1.242</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1439,40 +1439,40 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.39</v>
+        <v>37.14</v>
       </c>
       <c r="E19" t="n">
-        <v>13</v>
+        <v>4.6</v>
       </c>
       <c r="F19" t="n">
-        <v>0.03</v>
+        <v>8.074</v>
       </c>
       <c r="G19" t="n">
-        <v>0.07000000000000001</v>
+        <v>17.681</v>
       </c>
       <c r="H19" t="n">
-        <v>5.54</v>
+        <v>2.1</v>
       </c>
       <c r="I19" t="n">
-        <v>134.7</v>
+        <v>119</v>
       </c>
       <c r="J19" t="n">
-        <v>7.69</v>
+        <v>21.74</v>
       </c>
       <c r="K19" t="n">
-        <v>1.242</v>
+        <v>1.771</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1493,40 +1493,40 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>lng</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>37.14</v>
+        <v>29.3</v>
       </c>
       <c r="E20" t="n">
-        <v>4.6</v>
+        <v>14.1</v>
       </c>
       <c r="F20" t="n">
-        <v>8.074</v>
+        <v>2.078</v>
       </c>
       <c r="G20" t="n">
-        <v>17.681</v>
+        <v>3.74</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1</v>
+        <v>7.83</v>
       </c>
       <c r="I20" t="n">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="J20" t="n">
-        <v>21.74</v>
+        <v>7.09</v>
       </c>
       <c r="K20" t="n">
-        <v>1.771</v>
+        <v>0.706</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>below-mid</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>BWLP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1547,40 +1547,40 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>lpg</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>29.3</v>
+        <v>18.52</v>
       </c>
       <c r="E21" t="n">
-        <v>14.1</v>
+        <v>9.9</v>
       </c>
       <c r="F21" t="n">
-        <v>2.078</v>
+        <v>1.871</v>
       </c>
       <c r="G21" t="n">
-        <v>3.74</v>
+        <v>3.229</v>
       </c>
       <c r="H21" t="n">
-        <v>7.83</v>
+        <v>5.74</v>
       </c>
       <c r="I21" t="n">
-        <v>80</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>7.09</v>
+        <v>10.1</v>
       </c>
       <c r="K21" t="n">
-        <v>0.706</v>
+        <v>1.59</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>below-mid</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BWLP</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1601,32 +1601,32 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>lpg</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>18.52</v>
+        <v>73</v>
       </c>
       <c r="E22" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="F22" t="n">
-        <v>1.871</v>
+        <v>6.577</v>
       </c>
       <c r="G22" t="n">
-        <v>3.229</v>
+        <v>11.291</v>
       </c>
       <c r="H22" t="n">
-        <v>5.74</v>
+        <v>6.47</v>
       </c>
       <c r="I22" t="n">
-        <v>72.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="J22" t="n">
-        <v>10.1</v>
+        <v>9.01</v>
       </c>
       <c r="K22" t="n">
-        <v>1.59</v>
+        <v>1.732</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1699,7 +1699,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1709,40 +1709,40 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>lpg</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>36</v>
+        <v>25.2</v>
       </c>
       <c r="E24" t="n">
-        <v>9.300000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="F24" t="n">
-        <v>3.871</v>
+        <v>3.937</v>
       </c>
       <c r="G24" t="n">
-        <v>5.753</v>
+        <v>5.67</v>
       </c>
       <c r="H24" t="n">
-        <v>6.26</v>
+        <v>4.44</v>
       </c>
       <c r="I24" t="n">
-        <v>48.6</v>
+        <v>44</v>
       </c>
       <c r="J24" t="n">
-        <v>10.75</v>
+        <v>15.62</v>
       </c>
       <c r="K24" t="n">
-        <v>1.59</v>
+        <v>1.481</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1763,32 +1763,32 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>containerships</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25.2</v>
+        <v>38.99</v>
       </c>
       <c r="E25" t="n">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="F25" t="n">
-        <v>3.937</v>
+        <v>10.261</v>
       </c>
       <c r="G25" t="n">
-        <v>5.67</v>
+        <v>14.083</v>
       </c>
       <c r="H25" t="n">
-        <v>4.44</v>
+        <v>2.77</v>
       </c>
       <c r="I25" t="n">
-        <v>44</v>
+        <v>37.3</v>
       </c>
       <c r="J25" t="n">
-        <v>15.62</v>
+        <v>26.32</v>
       </c>
       <c r="K25" t="n">
-        <v>1.481</v>
+        <v>1.488</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1817,44 +1817,44 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>containerships</t>
+          <t>lpg</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>38.99</v>
+        <v>36</v>
       </c>
       <c r="E26" t="n">
-        <v>3.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>10.261</v>
+        <v>3.871</v>
       </c>
       <c r="G26" t="n">
-        <v>14.083</v>
+        <v>4.357</v>
       </c>
       <c r="H26" t="n">
-        <v>2.77</v>
+        <v>8.26</v>
       </c>
       <c r="I26" t="n">
-        <v>37.3</v>
+        <v>12.6</v>
       </c>
       <c r="J26" t="n">
-        <v>26.32</v>
+        <v>10.75</v>
       </c>
       <c r="K26" t="n">
-        <v>1.488</v>
+        <v>1.59</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>earnings-driven (tool&gt;cons)</t>
+          <t>earnings-aligned</t>
         </is>
       </c>
     </row>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -781,7 +781,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -791,40 +791,40 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>lng</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.2</v>
+        <v>21.6</v>
       </c>
       <c r="E7" t="n">
-        <v>9.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="F7" t="n">
-        <v>1.849</v>
+        <v>2.667</v>
       </c>
       <c r="G7" t="n">
-        <v>5.514</v>
+        <v>7.948</v>
       </c>
       <c r="H7" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="I7" t="n">
-        <v>198.1</v>
+        <v>198</v>
       </c>
       <c r="J7" t="n">
-        <v>10.75</v>
+        <v>12.35</v>
       </c>
       <c r="K7" t="n">
-        <v>2.788</v>
+        <v>0.781</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>below-mid</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -845,40 +845,40 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21.6</v>
+        <v>17.2</v>
       </c>
       <c r="E8" t="n">
-        <v>8.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>2.667</v>
+        <v>1.849</v>
       </c>
       <c r="G8" t="n">
-        <v>7.948</v>
+        <v>5.508</v>
       </c>
       <c r="H8" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="I8" t="n">
-        <v>198</v>
+        <v>197.8</v>
       </c>
       <c r="J8" t="n">
-        <v>12.35</v>
+        <v>10.75</v>
       </c>
       <c r="K8" t="n">
-        <v>0.781</v>
+        <v>2.788</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>below-mid</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1020,19 +1020,19 @@
         <v>1.725</v>
       </c>
       <c r="G11" t="n">
-        <v>4.794</v>
+        <v>4.888</v>
       </c>
       <c r="H11" t="n">
-        <v>5.11</v>
+        <v>5.01</v>
       </c>
       <c r="I11" t="n">
-        <v>177.9</v>
+        <v>183.3</v>
       </c>
       <c r="J11" t="n">
         <v>7.04</v>
       </c>
       <c r="K11" t="n">
-        <v>1.435</v>
+        <v>1.439</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1398,19 +1398,19 @@
         <v>0.03</v>
       </c>
       <c r="G18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>5.54</v>
+        <v>5.43</v>
       </c>
       <c r="I18" t="n">
-        <v>134.7</v>
+        <v>139.4</v>
       </c>
       <c r="J18" t="n">
         <v>7.69</v>
       </c>
       <c r="K18" t="n">
-        <v>1.242</v>
+        <v>1.241</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1722,19 +1722,19 @@
         <v>3.937</v>
       </c>
       <c r="G24" t="n">
-        <v>5.67</v>
+        <v>5.799</v>
       </c>
       <c r="H24" t="n">
-        <v>4.44</v>
+        <v>4.35</v>
       </c>
       <c r="I24" t="n">
-        <v>44</v>
+        <v>47.3</v>
       </c>
       <c r="J24" t="n">
         <v>15.62</v>
       </c>
       <c r="K24" t="n">
-        <v>1.481</v>
+        <v>1.479</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1236,19 +1236,19 @@
         <v>1.643</v>
       </c>
       <c r="G15" t="n">
-        <v>4.225</v>
+        <v>4.215</v>
       </c>
       <c r="H15" t="n">
-        <v>4.08</v>
+        <v>4.09</v>
       </c>
       <c r="I15" t="n">
-        <v>157.2</v>
+        <v>156.5</v>
       </c>
       <c r="J15" t="n">
         <v>9.52</v>
       </c>
       <c r="K15" t="n">
-        <v>1.445</v>
+        <v>1.443</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -943,7 +943,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -953,40 +953,40 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>36.8</v>
+        <v>24.5</v>
       </c>
       <c r="E10" t="n">
-        <v>9.4</v>
+        <v>14.2</v>
       </c>
       <c r="F10" t="n">
-        <v>3.915</v>
+        <v>1.725</v>
       </c>
       <c r="G10" t="n">
-        <v>11.308</v>
+        <v>4.989</v>
       </c>
       <c r="H10" t="n">
-        <v>3.25</v>
+        <v>4.91</v>
       </c>
       <c r="I10" t="n">
-        <v>188.8</v>
+        <v>189.2</v>
       </c>
       <c r="J10" t="n">
-        <v>10.64</v>
+        <v>7.04</v>
       </c>
       <c r="K10" t="n">
-        <v>2.573</v>
+        <v>1.284</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1007,40 +1007,40 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>24.5</v>
+        <v>36.8</v>
       </c>
       <c r="E11" t="n">
-        <v>14.2</v>
+        <v>9.4</v>
       </c>
       <c r="F11" t="n">
-        <v>1.725</v>
+        <v>3.915</v>
       </c>
       <c r="G11" t="n">
-        <v>4.888</v>
+        <v>11.308</v>
       </c>
       <c r="H11" t="n">
-        <v>5.01</v>
+        <v>3.25</v>
       </c>
       <c r="I11" t="n">
-        <v>183.3</v>
+        <v>188.8</v>
       </c>
       <c r="J11" t="n">
-        <v>7.04</v>
+        <v>10.64</v>
       </c>
       <c r="K11" t="n">
-        <v>1.439</v>
+        <v>2.573</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1169,40 +1169,40 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>67.59999999999999</v>
+        <v>17.25</v>
       </c>
       <c r="E14" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="F14" t="n">
-        <v>8.048</v>
+        <v>1.643</v>
       </c>
       <c r="G14" t="n">
-        <v>21.335</v>
+        <v>4.362</v>
       </c>
       <c r="H14" t="n">
-        <v>3.17</v>
+        <v>3.96</v>
       </c>
       <c r="I14" t="n">
-        <v>165.1</v>
+        <v>165.5</v>
       </c>
       <c r="J14" t="n">
-        <v>11.9</v>
+        <v>9.52</v>
       </c>
       <c r="K14" t="n">
-        <v>1.903</v>
+        <v>1.306</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1223,40 +1223,40 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17.25</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="F15" t="n">
-        <v>1.643</v>
+        <v>8.048</v>
       </c>
       <c r="G15" t="n">
-        <v>4.215</v>
+        <v>21.335</v>
       </c>
       <c r="H15" t="n">
-        <v>4.09</v>
+        <v>3.17</v>
       </c>
       <c r="I15" t="n">
-        <v>156.5</v>
+        <v>165.1</v>
       </c>
       <c r="J15" t="n">
-        <v>9.52</v>
+        <v>11.9</v>
       </c>
       <c r="K15" t="n">
-        <v>1.443</v>
+        <v>1.903</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1290,19 +1290,19 @@
         <v>0.799</v>
       </c>
       <c r="G16" t="n">
-        <v>2.047</v>
+        <v>2.079</v>
       </c>
       <c r="H16" t="n">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
       <c r="I16" t="n">
-        <v>156.2</v>
+        <v>160.3</v>
       </c>
       <c r="J16" t="n">
         <v>12.5</v>
       </c>
       <c r="K16" t="n">
-        <v>1.592</v>
+        <v>1.508</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1344,19 +1344,19 @@
         <v>1.64</v>
       </c>
       <c r="G17" t="n">
-        <v>3.952</v>
+        <v>4.023</v>
       </c>
       <c r="H17" t="n">
-        <v>3.69</v>
+        <v>3.63</v>
       </c>
       <c r="I17" t="n">
-        <v>140.9</v>
+        <v>145.2</v>
       </c>
       <c r="J17" t="n">
         <v>11.24</v>
       </c>
       <c r="K17" t="n">
-        <v>1.739</v>
+        <v>1.637</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1398,27 +1398,27 @@
         <v>0.03</v>
       </c>
       <c r="G18" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.073</v>
       </c>
       <c r="H18" t="n">
-        <v>5.43</v>
+        <v>5.32</v>
       </c>
       <c r="I18" t="n">
-        <v>139.4</v>
+        <v>144.5</v>
       </c>
       <c r="J18" t="n">
         <v>7.69</v>
       </c>
       <c r="K18" t="n">
-        <v>1.241</v>
+        <v>1.167</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>mid-cycle</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1722,19 +1722,19 @@
         <v>3.937</v>
       </c>
       <c r="G24" t="n">
-        <v>5.799</v>
+        <v>5.97</v>
       </c>
       <c r="H24" t="n">
-        <v>4.35</v>
+        <v>4.22</v>
       </c>
       <c r="I24" t="n">
-        <v>47.3</v>
+        <v>51.6</v>
       </c>
       <c r="J24" t="n">
         <v>15.62</v>
       </c>
       <c r="K24" t="n">
-        <v>1.479</v>
+        <v>1.351</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1788,15 +1788,15 @@
         <v>26.32</v>
       </c>
       <c r="K25" t="n">
-        <v>1.488</v>
+        <v>1.505</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -534,19 +534,19 @@
         <v>0.302</v>
       </c>
       <c r="G2" t="n">
-        <v>1.452</v>
+        <v>1.515</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="I2" t="n">
-        <v>380.5</v>
+        <v>401.5</v>
       </c>
       <c r="J2" t="n">
         <v>5.21</v>
       </c>
       <c r="K2" t="n">
-        <v>2.207</v>
+        <v>2.092</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -588,19 +588,19 @@
         <v>0.859</v>
       </c>
       <c r="G3" t="n">
-        <v>3.602</v>
+        <v>2.905</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7</v>
+        <v>4.58</v>
       </c>
       <c r="I3" t="n">
-        <v>319.4</v>
+        <v>238.3</v>
       </c>
       <c r="J3" t="n">
         <v>6.45</v>
       </c>
       <c r="K3" t="n">
-        <v>2.454</v>
+        <v>2.316</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -629,32 +629,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5.3</v>
+        <v>14.9</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>13.2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.279</v>
+        <v>1.129</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>3.588</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3</v>
+        <v>4.15</v>
       </c>
       <c r="I4" t="n">
-        <v>258.4</v>
+        <v>217.9</v>
       </c>
       <c r="J4" t="n">
-        <v>5.26</v>
+        <v>7.58</v>
       </c>
       <c r="K4" t="n">
-        <v>2.788</v>
+        <v>1.677</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -673,42 +673,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid proxy)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>27.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>9.300000000000001</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>2.978</v>
+        <v>6.867</v>
       </c>
       <c r="G5" t="n">
-        <v>9.609</v>
+        <v>20.633</v>
       </c>
       <c r="H5" t="n">
-        <v>2.88</v>
+        <v>3.99</v>
       </c>
       <c r="I5" t="n">
-        <v>222.6</v>
+        <v>200.5</v>
       </c>
       <c r="J5" t="n">
-        <v>10.75</v>
+        <v>8.33</v>
       </c>
       <c r="K5" t="n">
-        <v>1.686</v>
+        <v>2.101</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -727,50 +727,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid proxy)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>lng</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>82.40000000000001</v>
+        <v>21.6</v>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>8.1</v>
       </c>
       <c r="F6" t="n">
-        <v>6.867</v>
+        <v>2.667</v>
       </c>
       <c r="G6" t="n">
-        <v>21.722</v>
+        <v>7.948</v>
       </c>
       <c r="H6" t="n">
-        <v>3.79</v>
+        <v>2.72</v>
       </c>
       <c r="I6" t="n">
-        <v>216.3</v>
+        <v>198</v>
       </c>
       <c r="J6" t="n">
-        <v>8.33</v>
+        <v>12.35</v>
       </c>
       <c r="K6" t="n">
-        <v>2.111</v>
+        <v>0.781</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>below-mid</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -791,40 +791,40 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21.6</v>
+        <v>5.3</v>
       </c>
       <c r="E7" t="n">
-        <v>8.1</v>
+        <v>19</v>
       </c>
       <c r="F7" t="n">
-        <v>2.667</v>
+        <v>0.279</v>
       </c>
       <c r="G7" t="n">
-        <v>7.948</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>2.72</v>
+        <v>6.49</v>
       </c>
       <c r="I7" t="n">
-        <v>198</v>
+        <v>192.7</v>
       </c>
       <c r="J7" t="n">
-        <v>12.35</v>
+        <v>5.26</v>
       </c>
       <c r="K7" t="n">
-        <v>0.781</v>
+        <v>2.643</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>below-mid</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -845,40 +845,40 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.2</v>
+        <v>24.5</v>
       </c>
       <c r="E8" t="n">
-        <v>9.300000000000001</v>
+        <v>14.2</v>
       </c>
       <c r="F8" t="n">
-        <v>1.849</v>
+        <v>1.725</v>
       </c>
       <c r="G8" t="n">
-        <v>5.508</v>
+        <v>4.989</v>
       </c>
       <c r="H8" t="n">
-        <v>3.12</v>
+        <v>4.91</v>
       </c>
       <c r="I8" t="n">
-        <v>197.8</v>
+        <v>189.2</v>
       </c>
       <c r="J8" t="n">
-        <v>10.75</v>
+        <v>7.04</v>
       </c>
       <c r="K8" t="n">
-        <v>2.788</v>
+        <v>1.284</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -903,28 +903,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>27.7</v>
       </c>
       <c r="E9" t="n">
-        <v>8.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.805</v>
+        <v>2.978</v>
       </c>
       <c r="G9" t="n">
-        <v>2.395</v>
+        <v>8.257</v>
       </c>
       <c r="H9" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="I9" t="n">
-        <v>197.6</v>
+        <v>177.2</v>
       </c>
       <c r="J9" t="n">
-        <v>11.49</v>
+        <v>10.75</v>
       </c>
       <c r="K9" t="n">
-        <v>1.665</v>
+        <v>1.845</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -953,40 +953,40 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>24.5</v>
+        <v>17.2</v>
       </c>
       <c r="E10" t="n">
-        <v>14.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>1.725</v>
+        <v>1.849</v>
       </c>
       <c r="G10" t="n">
-        <v>4.989</v>
+        <v>5.028</v>
       </c>
       <c r="H10" t="n">
-        <v>4.91</v>
+        <v>3.42</v>
       </c>
       <c r="I10" t="n">
-        <v>189.2</v>
+        <v>171.9</v>
       </c>
       <c r="J10" t="n">
-        <v>7.04</v>
+        <v>10.75</v>
       </c>
       <c r="K10" t="n">
-        <v>1.284</v>
+        <v>2.643</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1007,40 +1007,40 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>36.8</v>
+        <v>17.25</v>
       </c>
       <c r="E11" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="F11" t="n">
-        <v>3.915</v>
+        <v>1.643</v>
       </c>
       <c r="G11" t="n">
-        <v>11.308</v>
+        <v>4.362</v>
       </c>
       <c r="H11" t="n">
-        <v>3.25</v>
+        <v>3.96</v>
       </c>
       <c r="I11" t="n">
-        <v>188.8</v>
+        <v>165.5</v>
       </c>
       <c r="J11" t="n">
-        <v>10.64</v>
+        <v>9.52</v>
       </c>
       <c r="K11" t="n">
-        <v>2.573</v>
+        <v>1.306</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1061,40 +1061,40 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.9</v>
+        <v>53.1</v>
       </c>
       <c r="E12" t="n">
-        <v>13.2</v>
+        <v>9.4</v>
       </c>
       <c r="F12" t="n">
-        <v>1.129</v>
+        <v>5.649</v>
       </c>
       <c r="G12" t="n">
-        <v>3.086</v>
+        <v>14.821</v>
       </c>
       <c r="H12" t="n">
-        <v>4.83</v>
+        <v>3.58</v>
       </c>
       <c r="I12" t="n">
-        <v>173.4</v>
+        <v>162.4</v>
       </c>
       <c r="J12" t="n">
-        <v>7.58</v>
+        <v>10.64</v>
       </c>
       <c r="K12" t="n">
-        <v>1.375</v>
+        <v>2.379</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1119,28 +1119,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>53.1</v>
+        <v>36.8</v>
       </c>
       <c r="E13" t="n">
         <v>9.4</v>
       </c>
       <c r="F13" t="n">
-        <v>5.649</v>
+        <v>3.915</v>
       </c>
       <c r="G13" t="n">
-        <v>15.298</v>
+        <v>10.235</v>
       </c>
       <c r="H13" t="n">
-        <v>3.47</v>
+        <v>3.6</v>
       </c>
       <c r="I13" t="n">
-        <v>170.8</v>
+        <v>161.4</v>
       </c>
       <c r="J13" t="n">
         <v>10.64</v>
       </c>
       <c r="K13" t="n">
-        <v>2.51</v>
+        <v>2.43</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1173,36 +1173,36 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.25</v>
+        <v>6.39</v>
       </c>
       <c r="E14" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="F14" t="n">
-        <v>1.643</v>
+        <v>0.799</v>
       </c>
       <c r="G14" t="n">
-        <v>4.362</v>
+        <v>2.079</v>
       </c>
       <c r="H14" t="n">
-        <v>3.96</v>
+        <v>3.07</v>
       </c>
       <c r="I14" t="n">
-        <v>165.5</v>
+        <v>160.3</v>
       </c>
       <c r="J14" t="n">
-        <v>9.52</v>
+        <v>12.5</v>
       </c>
       <c r="K14" t="n">
-        <v>1.306</v>
+        <v>1.508</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1227,28 +1227,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>67.59999999999999</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="F15" t="n">
-        <v>8.048</v>
+        <v>1.64</v>
       </c>
       <c r="G15" t="n">
-        <v>21.335</v>
+        <v>4.031</v>
       </c>
       <c r="H15" t="n">
-        <v>3.17</v>
+        <v>3.62</v>
       </c>
       <c r="I15" t="n">
-        <v>165.1</v>
+        <v>145.7</v>
       </c>
       <c r="J15" t="n">
-        <v>11.9</v>
+        <v>11.24</v>
       </c>
       <c r="K15" t="n">
-        <v>1.903</v>
+        <v>1.605</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1281,36 +1281,36 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6.39</v>
+        <v>0.39</v>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F16" t="n">
-        <v>0.799</v>
+        <v>0.03</v>
       </c>
       <c r="G16" t="n">
-        <v>2.079</v>
+        <v>0.073</v>
       </c>
       <c r="H16" t="n">
-        <v>3.07</v>
+        <v>5.32</v>
       </c>
       <c r="I16" t="n">
-        <v>160.3</v>
+        <v>144.5</v>
       </c>
       <c r="J16" t="n">
-        <v>12.5</v>
+        <v>7.69</v>
       </c>
       <c r="K16" t="n">
-        <v>1.508</v>
+        <v>1.167</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>mid-cycle</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>1.64</v>
+        <v>0.805</v>
       </c>
       <c r="G17" t="n">
-        <v>4.023</v>
+        <v>1.957</v>
       </c>
       <c r="H17" t="n">
-        <v>3.63</v>
+        <v>3.58</v>
       </c>
       <c r="I17" t="n">
-        <v>145.2</v>
+        <v>143.3</v>
       </c>
       <c r="J17" t="n">
-        <v>11.24</v>
+        <v>11.49</v>
       </c>
       <c r="K17" t="n">
-        <v>1.637</v>
+        <v>1.794</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1385,40 +1385,40 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.39</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="F18" t="n">
-        <v>0.03</v>
+        <v>8.048</v>
       </c>
       <c r="G18" t="n">
-        <v>0.073</v>
+        <v>18.535</v>
       </c>
       <c r="H18" t="n">
-        <v>5.32</v>
+        <v>3.65</v>
       </c>
       <c r="I18" t="n">
-        <v>144.5</v>
+        <v>130.3</v>
       </c>
       <c r="J18" t="n">
-        <v>7.69</v>
+        <v>11.9</v>
       </c>
       <c r="K18" t="n">
-        <v>1.167</v>
+        <v>1.781</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>mid-cycle</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1452,19 +1452,19 @@
         <v>8.074</v>
       </c>
       <c r="G19" t="n">
-        <v>17.681</v>
+        <v>15.876</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="I19" t="n">
-        <v>119</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="J19" t="n">
         <v>21.74</v>
       </c>
       <c r="K19" t="n">
-        <v>1.771</v>
+        <v>1.669</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1601,40 +1601,40 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>containerships</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>73</v>
+        <v>2.44</v>
       </c>
       <c r="E22" t="n">
-        <v>11.1</v>
+        <v>7.7</v>
       </c>
       <c r="F22" t="n">
-        <v>6.577</v>
+        <v>0.317</v>
       </c>
       <c r="G22" t="n">
-        <v>11.291</v>
+        <v>0.541</v>
       </c>
       <c r="H22" t="n">
-        <v>6.47</v>
+        <v>4.51</v>
       </c>
       <c r="I22" t="n">
-        <v>71.7</v>
+        <v>70.8</v>
       </c>
       <c r="J22" t="n">
-        <v>9.01</v>
+        <v>12.99</v>
       </c>
       <c r="K22" t="n">
-        <v>1.732</v>
+        <v>1.317</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1655,32 +1655,32 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>containerships</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2.44</v>
+        <v>25.2</v>
       </c>
       <c r="E23" t="n">
-        <v>7.7</v>
+        <v>6.4</v>
       </c>
       <c r="F23" t="n">
-        <v>0.317</v>
+        <v>3.937</v>
       </c>
       <c r="G23" t="n">
-        <v>0.541</v>
+        <v>5.97</v>
       </c>
       <c r="H23" t="n">
-        <v>4.51</v>
+        <v>4.22</v>
       </c>
       <c r="I23" t="n">
-        <v>70.8</v>
+        <v>51.6</v>
       </c>
       <c r="J23" t="n">
-        <v>12.99</v>
+        <v>15.62</v>
       </c>
       <c r="K23" t="n">
-        <v>1.317</v>
+        <v>1.351</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1709,40 +1709,40 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>25.2</v>
+        <v>73</v>
       </c>
       <c r="E24" t="n">
-        <v>6.4</v>
+        <v>11.1</v>
       </c>
       <c r="F24" t="n">
-        <v>3.937</v>
+        <v>6.577</v>
       </c>
       <c r="G24" t="n">
-        <v>5.97</v>
+        <v>9.677</v>
       </c>
       <c r="H24" t="n">
-        <v>4.22</v>
+        <v>7.54</v>
       </c>
       <c r="I24" t="n">
-        <v>51.6</v>
+        <v>47.1</v>
       </c>
       <c r="J24" t="n">
-        <v>15.62</v>
+        <v>9.01</v>
       </c>
       <c r="K24" t="n">
-        <v>1.351</v>
+        <v>1.807</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -565,7 +565,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -579,28 +579,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.31</v>
+        <v>5.3</v>
       </c>
       <c r="E3" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>0.859</v>
+        <v>0.279</v>
       </c>
       <c r="G3" t="n">
-        <v>2.905</v>
+        <v>1.064</v>
       </c>
       <c r="H3" t="n">
-        <v>4.58</v>
+        <v>4.98</v>
       </c>
       <c r="I3" t="n">
-        <v>238.3</v>
+        <v>281.5</v>
       </c>
       <c r="J3" t="n">
-        <v>6.45</v>
+        <v>5.26</v>
       </c>
       <c r="K3" t="n">
-        <v>2.316</v>
+        <v>2.643</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -629,32 +629,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.9</v>
+        <v>13.31</v>
       </c>
       <c r="E4" t="n">
-        <v>13.2</v>
+        <v>15.5</v>
       </c>
       <c r="F4" t="n">
-        <v>1.129</v>
+        <v>0.859</v>
       </c>
       <c r="G4" t="n">
-        <v>3.588</v>
+        <v>2.905</v>
       </c>
       <c r="H4" t="n">
-        <v>4.15</v>
+        <v>4.58</v>
       </c>
       <c r="I4" t="n">
-        <v>217.9</v>
+        <v>238.3</v>
       </c>
       <c r="J4" t="n">
-        <v>7.58</v>
+        <v>6.45</v>
       </c>
       <c r="K4" t="n">
-        <v>1.677</v>
+        <v>2.316</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -673,42 +673,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid proxy)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>82.40000000000001</v>
+        <v>14.9</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>13.2</v>
       </c>
       <c r="F5" t="n">
-        <v>6.867</v>
+        <v>1.129</v>
       </c>
       <c r="G5" t="n">
-        <v>20.633</v>
+        <v>3.588</v>
       </c>
       <c r="H5" t="n">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="I5" t="n">
-        <v>200.5</v>
+        <v>217.9</v>
       </c>
       <c r="J5" t="n">
-        <v>8.33</v>
+        <v>7.58</v>
       </c>
       <c r="K5" t="n">
-        <v>2.101</v>
+        <v>1.677</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -727,50 +727,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid proxy)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21.6</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>8.1</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>2.667</v>
+        <v>6.867</v>
       </c>
       <c r="G6" t="n">
-        <v>7.948</v>
+        <v>20.633</v>
       </c>
       <c r="H6" t="n">
-        <v>2.72</v>
+        <v>3.99</v>
       </c>
       <c r="I6" t="n">
-        <v>198</v>
+        <v>200.5</v>
       </c>
       <c r="J6" t="n">
-        <v>12.35</v>
+        <v>8.33</v>
       </c>
       <c r="K6" t="n">
-        <v>0.781</v>
+        <v>2.101</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>below-mid</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -791,40 +791,40 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>lng</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.3</v>
+        <v>21.6</v>
       </c>
       <c r="E7" t="n">
-        <v>19</v>
+        <v>8.1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.279</v>
+        <v>2.667</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8159999999999999</v>
+        <v>7.948</v>
       </c>
       <c r="H7" t="n">
-        <v>6.49</v>
+        <v>2.72</v>
       </c>
       <c r="I7" t="n">
-        <v>192.7</v>
+        <v>198</v>
       </c>
       <c r="J7" t="n">
-        <v>5.26</v>
+        <v>12.35</v>
       </c>
       <c r="K7" t="n">
-        <v>2.643</v>
+        <v>0.781</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>below-mid</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,28 +525,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.8</v>
+        <v>14.14</v>
       </c>
       <c r="E2" t="n">
-        <v>19.2</v>
+        <v>22.2</v>
       </c>
       <c r="F2" t="n">
-        <v>0.302</v>
+        <v>0.637</v>
       </c>
       <c r="G2" t="n">
-        <v>1.515</v>
+        <v>2.905</v>
       </c>
       <c r="H2" t="n">
-        <v>3.83</v>
+        <v>4.87</v>
       </c>
       <c r="I2" t="n">
-        <v>401.5</v>
+        <v>356.1</v>
       </c>
       <c r="J2" t="n">
-        <v>5.21</v>
+        <v>4.5</v>
       </c>
       <c r="K2" t="n">
-        <v>2.092</v>
+        <v>2.316</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -579,28 +579,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="E3" t="n">
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="F3" t="n">
-        <v>0.279</v>
+        <v>0.342</v>
       </c>
       <c r="G3" t="n">
-        <v>1.064</v>
+        <v>1.515</v>
       </c>
       <c r="H3" t="n">
-        <v>4.98</v>
+        <v>4.22</v>
       </c>
       <c r="I3" t="n">
-        <v>281.5</v>
+        <v>342.6</v>
       </c>
       <c r="J3" t="n">
-        <v>5.26</v>
+        <v>5.35</v>
       </c>
       <c r="K3" t="n">
-        <v>2.643</v>
+        <v>2.092</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -633,28 +633,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.31</v>
+        <v>6.32</v>
       </c>
       <c r="E4" t="n">
-        <v>15.5</v>
+        <v>22.6</v>
       </c>
       <c r="F4" t="n">
-        <v>0.859</v>
+        <v>0.28</v>
       </c>
       <c r="G4" t="n">
-        <v>2.905</v>
+        <v>1.064</v>
       </c>
       <c r="H4" t="n">
-        <v>4.58</v>
+        <v>5.94</v>
       </c>
       <c r="I4" t="n">
-        <v>238.3</v>
+        <v>280.5</v>
       </c>
       <c r="J4" t="n">
-        <v>6.45</v>
+        <v>4.42</v>
       </c>
       <c r="K4" t="n">
-        <v>2.316</v>
+        <v>2.643</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.9</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>13.2</v>
+        <v>15.5</v>
       </c>
       <c r="F5" t="n">
-        <v>1.129</v>
+        <v>1.097</v>
       </c>
       <c r="G5" t="n">
         <v>3.588</v>
       </c>
       <c r="H5" t="n">
-        <v>4.15</v>
+        <v>4.74</v>
       </c>
       <c r="I5" t="n">
-        <v>217.9</v>
+        <v>227.2</v>
       </c>
       <c r="J5" t="n">
-        <v>7.58</v>
+        <v>6.45</v>
       </c>
       <c r="K5" t="n">
         <v>1.677</v>
@@ -741,25 +741,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>82.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>12.8</v>
       </c>
       <c r="F6" t="n">
-        <v>6.867</v>
+        <v>7.281</v>
       </c>
       <c r="G6" t="n">
         <v>20.633</v>
       </c>
       <c r="H6" t="n">
-        <v>3.99</v>
+        <v>4.52</v>
       </c>
       <c r="I6" t="n">
-        <v>200.5</v>
+        <v>183.4</v>
       </c>
       <c r="J6" t="n">
-        <v>8.33</v>
+        <v>7.81</v>
       </c>
       <c r="K6" t="n">
         <v>2.101</v>
@@ -781,7 +781,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -791,40 +791,40 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21.6</v>
+        <v>29.5</v>
       </c>
       <c r="E7" t="n">
-        <v>8.1</v>
+        <v>9.9</v>
       </c>
       <c r="F7" t="n">
-        <v>2.667</v>
+        <v>2.98</v>
       </c>
       <c r="G7" t="n">
-        <v>7.948</v>
+        <v>8.257</v>
       </c>
       <c r="H7" t="n">
-        <v>2.72</v>
+        <v>3.57</v>
       </c>
       <c r="I7" t="n">
-        <v>198</v>
+        <v>177.1</v>
       </c>
       <c r="J7" t="n">
-        <v>12.35</v>
+        <v>10.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0.781</v>
+        <v>1.845</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>below-mid</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -845,40 +845,40 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>lng</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>24.5</v>
+        <v>22.8</v>
       </c>
       <c r="E8" t="n">
-        <v>14.2</v>
+        <v>7.9</v>
       </c>
       <c r="F8" t="n">
-        <v>1.725</v>
+        <v>2.886</v>
       </c>
       <c r="G8" t="n">
-        <v>4.989</v>
+        <v>7.948</v>
       </c>
       <c r="H8" t="n">
-        <v>4.91</v>
+        <v>2.87</v>
       </c>
       <c r="I8" t="n">
-        <v>189.2</v>
+        <v>175.4</v>
       </c>
       <c r="J8" t="n">
-        <v>7.04</v>
+        <v>12.66</v>
       </c>
       <c r="K8" t="n">
-        <v>1.284</v>
+        <v>0.781</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>below-mid</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -899,40 +899,40 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>27.7</v>
+        <v>25.1</v>
       </c>
       <c r="E9" t="n">
-        <v>9.300000000000001</v>
+        <v>13.7</v>
       </c>
       <c r="F9" t="n">
-        <v>2.978</v>
+        <v>1.832</v>
       </c>
       <c r="G9" t="n">
-        <v>8.257</v>
+        <v>4.989</v>
       </c>
       <c r="H9" t="n">
-        <v>3.35</v>
+        <v>5.03</v>
       </c>
       <c r="I9" t="n">
-        <v>177.2</v>
+        <v>172.3</v>
       </c>
       <c r="J9" t="n">
-        <v>10.75</v>
+        <v>7.3</v>
       </c>
       <c r="K9" t="n">
-        <v>1.845</v>
+        <v>1.284</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -953,40 +953,40 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.2</v>
+        <v>17.25</v>
       </c>
       <c r="E10" t="n">
-        <v>9.300000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="F10" t="n">
-        <v>1.849</v>
+        <v>1.643</v>
       </c>
       <c r="G10" t="n">
-        <v>5.028</v>
+        <v>4.362</v>
       </c>
       <c r="H10" t="n">
-        <v>3.42</v>
+        <v>3.96</v>
       </c>
       <c r="I10" t="n">
-        <v>171.9</v>
+        <v>165.5</v>
       </c>
       <c r="J10" t="n">
-        <v>10.75</v>
+        <v>9.52</v>
       </c>
       <c r="K10" t="n">
-        <v>2.643</v>
+        <v>1.306</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1007,40 +1007,40 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.25</v>
+        <v>18.4</v>
       </c>
       <c r="E11" t="n">
-        <v>10.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>1.643</v>
+        <v>1.897</v>
       </c>
       <c r="G11" t="n">
-        <v>4.362</v>
+        <v>5.028</v>
       </c>
       <c r="H11" t="n">
-        <v>3.96</v>
+        <v>3.66</v>
       </c>
       <c r="I11" t="n">
-        <v>165.5</v>
+        <v>165.1</v>
       </c>
       <c r="J11" t="n">
-        <v>9.52</v>
+        <v>10.31</v>
       </c>
       <c r="K11" t="n">
-        <v>1.306</v>
+        <v>2.643</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1061,32 +1061,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>53.1</v>
+        <v>6.39</v>
       </c>
       <c r="E12" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
-        <v>5.649</v>
+        <v>0.799</v>
       </c>
       <c r="G12" t="n">
-        <v>14.821</v>
+        <v>2.079</v>
       </c>
       <c r="H12" t="n">
-        <v>3.58</v>
+        <v>3.07</v>
       </c>
       <c r="I12" t="n">
-        <v>162.4</v>
+        <v>160.3</v>
       </c>
       <c r="J12" t="n">
-        <v>10.64</v>
+        <v>12.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.379</v>
+        <v>1.508</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1119,25 +1119,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>36.8</v>
+        <v>39.6</v>
       </c>
       <c r="E13" t="n">
-        <v>9.4</v>
+        <v>9.9</v>
       </c>
       <c r="F13" t="n">
-        <v>3.915</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
         <v>10.235</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6</v>
+        <v>3.87</v>
       </c>
       <c r="I13" t="n">
-        <v>161.4</v>
+        <v>155.9</v>
       </c>
       <c r="J13" t="n">
-        <v>10.64</v>
+        <v>10.1</v>
       </c>
       <c r="K13" t="n">
         <v>2.43</v>
@@ -1159,7 +1159,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1169,32 +1169,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6.39</v>
+        <v>63.8</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>10.9</v>
       </c>
       <c r="F14" t="n">
-        <v>0.799</v>
+        <v>5.853</v>
       </c>
       <c r="G14" t="n">
-        <v>2.079</v>
+        <v>14.821</v>
       </c>
       <c r="H14" t="n">
-        <v>3.07</v>
+        <v>4.3</v>
       </c>
       <c r="I14" t="n">
-        <v>160.3</v>
+        <v>153.2</v>
       </c>
       <c r="J14" t="n">
-        <v>12.5</v>
+        <v>9.17</v>
       </c>
       <c r="K14" t="n">
-        <v>1.508</v>
+        <v>2.379</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1227,25 +1227,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>16.4</v>
       </c>
       <c r="E15" t="n">
-        <v>8.9</v>
+        <v>10.2</v>
       </c>
       <c r="F15" t="n">
-        <v>1.64</v>
+        <v>1.608</v>
       </c>
       <c r="G15" t="n">
         <v>4.031</v>
       </c>
       <c r="H15" t="n">
-        <v>3.62</v>
+        <v>4.07</v>
       </c>
       <c r="I15" t="n">
-        <v>145.7</v>
+        <v>150.7</v>
       </c>
       <c r="J15" t="n">
-        <v>11.24</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K15" t="n">
         <v>1.605</v>
@@ -1267,7 +1267,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1277,40 +1277,40 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.39</v>
+        <v>7.6</v>
       </c>
       <c r="E16" t="n">
-        <v>13</v>
+        <v>9.5</v>
       </c>
       <c r="F16" t="n">
-        <v>0.03</v>
+        <v>0.8</v>
       </c>
       <c r="G16" t="n">
-        <v>0.073</v>
+        <v>1.957</v>
       </c>
       <c r="H16" t="n">
-        <v>5.32</v>
+        <v>3.88</v>
       </c>
       <c r="I16" t="n">
-        <v>144.5</v>
+        <v>144.7</v>
       </c>
       <c r="J16" t="n">
-        <v>7.69</v>
+        <v>10.53</v>
       </c>
       <c r="K16" t="n">
-        <v>1.167</v>
+        <v>1.794</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>mid-cycle</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1331,40 +1331,40 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>0.39</v>
       </c>
       <c r="E17" t="n">
-        <v>8.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="F17" t="n">
-        <v>0.805</v>
+        <v>0.03</v>
       </c>
       <c r="G17" t="n">
-        <v>1.957</v>
+        <v>0.073</v>
       </c>
       <c r="H17" t="n">
-        <v>3.58</v>
+        <v>5.32</v>
       </c>
       <c r="I17" t="n">
-        <v>143.3</v>
+        <v>144.5</v>
       </c>
       <c r="J17" t="n">
-        <v>11.49</v>
+        <v>7.69</v>
       </c>
       <c r="K17" t="n">
-        <v>1.794</v>
+        <v>1.167</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>mid-cycle</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1389,25 +1389,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>67.59999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="F18" t="n">
-        <v>8.048</v>
+        <v>8.663</v>
       </c>
       <c r="G18" t="n">
         <v>18.535</v>
       </c>
       <c r="H18" t="n">
-        <v>3.65</v>
+        <v>4.16</v>
       </c>
       <c r="I18" t="n">
-        <v>130.3</v>
+        <v>114</v>
       </c>
       <c r="J18" t="n">
-        <v>11.9</v>
+        <v>11.24</v>
       </c>
       <c r="K18" t="n">
         <v>1.781</v>
@@ -1497,25 +1497,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.3</v>
+        <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>14.1</v>
+        <v>14.9</v>
       </c>
       <c r="F20" t="n">
-        <v>2.078</v>
+        <v>2.081</v>
       </c>
       <c r="G20" t="n">
         <v>3.74</v>
       </c>
       <c r="H20" t="n">
-        <v>7.83</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>80</v>
+        <v>79.8</v>
       </c>
       <c r="J20" t="n">
-        <v>7.09</v>
+        <v>6.71</v>
       </c>
       <c r="K20" t="n">
         <v>0.706</v>
@@ -1551,25 +1551,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>18.52</v>
+        <v>21.77</v>
       </c>
       <c r="E21" t="n">
-        <v>9.9</v>
+        <v>11.6</v>
       </c>
       <c r="F21" t="n">
-        <v>1.871</v>
+        <v>1.877</v>
       </c>
       <c r="G21" t="n">
         <v>3.229</v>
       </c>
       <c r="H21" t="n">
-        <v>5.74</v>
+        <v>6.74</v>
       </c>
       <c r="I21" t="n">
-        <v>72.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="J21" t="n">
-        <v>10.1</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K21" t="n">
         <v>1.59</v>
@@ -1605,25 +1605,25 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="E22" t="n">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="F22" t="n">
-        <v>0.317</v>
+        <v>0.315</v>
       </c>
       <c r="G22" t="n">
         <v>0.541</v>
       </c>
       <c r="H22" t="n">
-        <v>4.51</v>
+        <v>4.71</v>
       </c>
       <c r="I22" t="n">
-        <v>70.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>12.99</v>
+        <v>12.35</v>
       </c>
       <c r="K22" t="n">
         <v>1.317</v>
@@ -1645,7 +1645,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1655,40 +1655,40 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>25.2</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="F23" t="n">
-        <v>3.937</v>
+        <v>5.877</v>
       </c>
       <c r="G23" t="n">
-        <v>5.97</v>
+        <v>9.677</v>
       </c>
       <c r="H23" t="n">
-        <v>4.22</v>
+        <v>7.89</v>
       </c>
       <c r="I23" t="n">
-        <v>51.6</v>
+        <v>64.7</v>
       </c>
       <c r="J23" t="n">
-        <v>15.62</v>
+        <v>7.69</v>
       </c>
       <c r="K23" t="n">
-        <v>1.351</v>
+        <v>1.807</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1709,40 +1709,40 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>73</v>
+        <v>28.6</v>
       </c>
       <c r="E24" t="n">
-        <v>11.1</v>
+        <v>7.2</v>
       </c>
       <c r="F24" t="n">
-        <v>6.577</v>
+        <v>3.972</v>
       </c>
       <c r="G24" t="n">
-        <v>9.677</v>
+        <v>5.97</v>
       </c>
       <c r="H24" t="n">
-        <v>7.54</v>
+        <v>4.79</v>
       </c>
       <c r="I24" t="n">
-        <v>47.1</v>
+        <v>50.3</v>
       </c>
       <c r="J24" t="n">
-        <v>9.01</v>
+        <v>13.89</v>
       </c>
       <c r="K24" t="n">
-        <v>1.807</v>
+        <v>1.351</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1821,25 +1821,25 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>36</v>
+        <v>44.4</v>
       </c>
       <c r="E26" t="n">
-        <v>9.300000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="F26" t="n">
-        <v>3.871</v>
+        <v>3.639</v>
       </c>
       <c r="G26" t="n">
         <v>4.357</v>
       </c>
       <c r="H26" t="n">
-        <v>8.26</v>
+        <v>10.19</v>
       </c>
       <c r="I26" t="n">
-        <v>12.6</v>
+        <v>19.7</v>
       </c>
       <c r="J26" t="n">
-        <v>10.75</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K26" t="n">
         <v>1.59</v>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -727,42 +727,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid proxy)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>93.2</v>
+        <v>29.5</v>
       </c>
       <c r="E6" t="n">
-        <v>12.8</v>
+        <v>9.9</v>
       </c>
       <c r="F6" t="n">
-        <v>7.281</v>
+        <v>2.98</v>
       </c>
       <c r="G6" t="n">
-        <v>20.633</v>
+        <v>8.631</v>
       </c>
       <c r="H6" t="n">
-        <v>4.52</v>
+        <v>3.42</v>
       </c>
       <c r="I6" t="n">
-        <v>183.4</v>
+        <v>189.7</v>
       </c>
       <c r="J6" t="n">
-        <v>7.81</v>
+        <v>10.1</v>
       </c>
       <c r="K6" t="n">
-        <v>2.101</v>
+        <v>1.844</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,42 +781,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid proxy)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>29.5</v>
+        <v>93.2</v>
       </c>
       <c r="E7" t="n">
-        <v>9.9</v>
+        <v>12.8</v>
       </c>
       <c r="F7" t="n">
-        <v>2.98</v>
+        <v>7.281</v>
       </c>
       <c r="G7" t="n">
-        <v>8.257</v>
+        <v>20.633</v>
       </c>
       <c r="H7" t="n">
-        <v>3.57</v>
+        <v>4.52</v>
       </c>
       <c r="I7" t="n">
-        <v>177.1</v>
+        <v>183.4</v>
       </c>
       <c r="J7" t="n">
-        <v>10.1</v>
+        <v>7.81</v>
       </c>
       <c r="K7" t="n">
-        <v>1.845</v>
+        <v>2.101</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -619,7 +619,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -629,32 +629,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6.32</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>22.6</v>
+        <v>15.5</v>
       </c>
       <c r="F4" t="n">
-        <v>0.28</v>
+        <v>1.097</v>
       </c>
       <c r="G4" t="n">
-        <v>1.064</v>
+        <v>3.588</v>
       </c>
       <c r="H4" t="n">
-        <v>5.94</v>
+        <v>4.74</v>
       </c>
       <c r="I4" t="n">
-        <v>280.5</v>
+        <v>227.2</v>
       </c>
       <c r="J4" t="n">
-        <v>4.42</v>
+        <v>6.45</v>
       </c>
       <c r="K4" t="n">
-        <v>2.643</v>
+        <v>1.677</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -683,32 +683,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>4.7</v>
       </c>
       <c r="E5" t="n">
-        <v>15.5</v>
+        <v>14.4</v>
       </c>
       <c r="F5" t="n">
-        <v>1.097</v>
+        <v>0.326</v>
       </c>
       <c r="G5" t="n">
-        <v>3.588</v>
+        <v>1.064</v>
       </c>
       <c r="H5" t="n">
-        <v>4.74</v>
+        <v>4.42</v>
       </c>
       <c r="I5" t="n">
-        <v>227.2</v>
+        <v>226</v>
       </c>
       <c r="J5" t="n">
-        <v>6.45</v>
+        <v>6.94</v>
       </c>
       <c r="K5" t="n">
-        <v>1.677</v>
+        <v>2.643</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -525,25 +525,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.14</v>
+        <v>16.06</v>
       </c>
       <c r="E2" t="n">
-        <v>22.2</v>
+        <v>25.5</v>
       </c>
       <c r="F2" t="n">
-        <v>0.637</v>
+        <v>0.63</v>
       </c>
       <c r="G2" t="n">
         <v>2.905</v>
       </c>
       <c r="H2" t="n">
-        <v>4.87</v>
+        <v>5.53</v>
       </c>
       <c r="I2" t="n">
-        <v>356.1</v>
+        <v>361.3</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5</v>
+        <v>3.92</v>
       </c>
       <c r="K2" t="n">
         <v>2.316</v>
@@ -579,25 +579,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="E3" t="n">
-        <v>18.7</v>
+        <v>17.7</v>
       </c>
       <c r="F3" t="n">
-        <v>0.342</v>
+        <v>0.384</v>
       </c>
       <c r="G3" t="n">
         <v>1.515</v>
       </c>
       <c r="H3" t="n">
-        <v>4.22</v>
+        <v>4.49</v>
       </c>
       <c r="I3" t="n">
-        <v>342.6</v>
+        <v>294.3</v>
       </c>
       <c r="J3" t="n">
-        <v>5.35</v>
+        <v>5.65</v>
       </c>
       <c r="K3" t="n">
         <v>2.092</v>
@@ -619,7 +619,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -629,32 +629,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>4.7</v>
       </c>
       <c r="E4" t="n">
-        <v>15.5</v>
+        <v>14.4</v>
       </c>
       <c r="F4" t="n">
-        <v>1.097</v>
+        <v>0.326</v>
       </c>
       <c r="G4" t="n">
-        <v>3.588</v>
+        <v>1.064</v>
       </c>
       <c r="H4" t="n">
-        <v>4.74</v>
+        <v>4.42</v>
       </c>
       <c r="I4" t="n">
-        <v>227.2</v>
+        <v>226</v>
       </c>
       <c r="J4" t="n">
-        <v>6.45</v>
+        <v>6.94</v>
       </c>
       <c r="K4" t="n">
-        <v>1.677</v>
+        <v>2.643</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -673,12 +673,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid proxy)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,28 +687,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.7</v>
+        <v>99.3</v>
       </c>
       <c r="E5" t="n">
-        <v>14.4</v>
+        <v>13.9</v>
       </c>
       <c r="F5" t="n">
-        <v>0.326</v>
+        <v>7.144</v>
       </c>
       <c r="G5" t="n">
-        <v>1.064</v>
+        <v>20.633</v>
       </c>
       <c r="H5" t="n">
-        <v>4.42</v>
+        <v>4.81</v>
       </c>
       <c r="I5" t="n">
-        <v>226</v>
+        <v>188.8</v>
       </c>
       <c r="J5" t="n">
-        <v>6.94</v>
+        <v>7.19</v>
       </c>
       <c r="K5" t="n">
-        <v>2.643</v>
+        <v>2.101</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -741,25 +741,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>29.5</v>
+        <v>31.8</v>
       </c>
       <c r="E6" t="n">
-        <v>9.9</v>
+        <v>10.6</v>
       </c>
       <c r="F6" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
         <v>8.631</v>
       </c>
       <c r="H6" t="n">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="I6" t="n">
-        <v>189.7</v>
+        <v>187.7</v>
       </c>
       <c r="J6" t="n">
-        <v>10.1</v>
+        <v>9.43</v>
       </c>
       <c r="K6" t="n">
         <v>1.844</v>
@@ -781,50 +781,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid proxy)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>lng</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>93.2</v>
+        <v>22.8</v>
       </c>
       <c r="E7" t="n">
-        <v>12.8</v>
+        <v>7.9</v>
       </c>
       <c r="F7" t="n">
-        <v>7.281</v>
+        <v>2.886</v>
       </c>
       <c r="G7" t="n">
-        <v>20.633</v>
+        <v>7.948</v>
       </c>
       <c r="H7" t="n">
-        <v>4.52</v>
+        <v>2.87</v>
       </c>
       <c r="I7" t="n">
-        <v>183.4</v>
+        <v>175.4</v>
       </c>
       <c r="J7" t="n">
-        <v>7.81</v>
+        <v>12.66</v>
       </c>
       <c r="K7" t="n">
-        <v>2.101</v>
+        <v>0.781</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>below-mid</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -845,40 +845,40 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>22.8</v>
+        <v>17.25</v>
       </c>
       <c r="E8" t="n">
-        <v>7.9</v>
+        <v>10.5</v>
       </c>
       <c r="F8" t="n">
-        <v>2.886</v>
+        <v>1.643</v>
       </c>
       <c r="G8" t="n">
-        <v>7.948</v>
+        <v>4.362</v>
       </c>
       <c r="H8" t="n">
-        <v>2.87</v>
+        <v>3.96</v>
       </c>
       <c r="I8" t="n">
-        <v>175.4</v>
+        <v>165.5</v>
       </c>
       <c r="J8" t="n">
-        <v>12.66</v>
+        <v>9.52</v>
       </c>
       <c r="K8" t="n">
-        <v>0.781</v>
+        <v>1.306</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>below-mid</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -899,40 +899,40 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>25.1</v>
+        <v>19.4</v>
       </c>
       <c r="E9" t="n">
-        <v>13.7</v>
+        <v>9.9</v>
       </c>
       <c r="F9" t="n">
-        <v>1.832</v>
+        <v>1.96</v>
       </c>
       <c r="G9" t="n">
-        <v>4.989</v>
+        <v>5.028</v>
       </c>
       <c r="H9" t="n">
-        <v>5.03</v>
+        <v>3.86</v>
       </c>
       <c r="I9" t="n">
-        <v>172.3</v>
+        <v>156.6</v>
       </c>
       <c r="J9" t="n">
-        <v>7.3</v>
+        <v>10.1</v>
       </c>
       <c r="K9" t="n">
-        <v>1.284</v>
+        <v>2.643</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -953,40 +953,40 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.25</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="F10" t="n">
-        <v>1.643</v>
+        <v>0.798</v>
       </c>
       <c r="G10" t="n">
-        <v>4.362</v>
+        <v>1.957</v>
       </c>
       <c r="H10" t="n">
-        <v>3.96</v>
+        <v>4.24</v>
       </c>
       <c r="I10" t="n">
-        <v>165.5</v>
+        <v>145.3</v>
       </c>
       <c r="J10" t="n">
-        <v>9.52</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>1.306</v>
+        <v>1.794</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1007,40 +1007,40 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.4</v>
+        <v>0.53</v>
       </c>
       <c r="E11" t="n">
-        <v>9.699999999999999</v>
+        <v>17.8</v>
       </c>
       <c r="F11" t="n">
-        <v>1.897</v>
+        <v>0.03</v>
       </c>
       <c r="G11" t="n">
-        <v>5.028</v>
+        <v>0.073</v>
       </c>
       <c r="H11" t="n">
-        <v>3.66</v>
+        <v>7.26</v>
       </c>
       <c r="I11" t="n">
-        <v>165.1</v>
+        <v>145.2</v>
       </c>
       <c r="J11" t="n">
-        <v>10.31</v>
+        <v>5.62</v>
       </c>
       <c r="K11" t="n">
-        <v>2.643</v>
+        <v>1.167</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>mid-cycle</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1061,32 +1061,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.39</v>
+        <v>43.8</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>10.3</v>
       </c>
       <c r="F12" t="n">
-        <v>0.799</v>
+        <v>4.252</v>
       </c>
       <c r="G12" t="n">
-        <v>2.079</v>
+        <v>10.235</v>
       </c>
       <c r="H12" t="n">
-        <v>3.07</v>
+        <v>4.28</v>
       </c>
       <c r="I12" t="n">
-        <v>160.3</v>
+        <v>140.7</v>
       </c>
       <c r="J12" t="n">
-        <v>12.5</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>1.508</v>
+        <v>2.43</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1115,40 +1115,40 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>39.6</v>
+        <v>25.8</v>
       </c>
       <c r="E13" t="n">
-        <v>9.9</v>
+        <v>12.3</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>2.098</v>
       </c>
       <c r="G13" t="n">
-        <v>10.235</v>
+        <v>4.989</v>
       </c>
       <c r="H13" t="n">
-        <v>3.87</v>
+        <v>5.17</v>
       </c>
       <c r="I13" t="n">
-        <v>155.9</v>
+        <v>137.9</v>
       </c>
       <c r="J13" t="n">
-        <v>10.1</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>2.43</v>
+        <v>1.284</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1173,28 +1173,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>63.8</v>
+        <v>18.3</v>
       </c>
       <c r="E14" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="F14" t="n">
-        <v>5.853</v>
+        <v>1.777</v>
       </c>
       <c r="G14" t="n">
-        <v>14.821</v>
+        <v>4.031</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3</v>
+        <v>4.54</v>
       </c>
       <c r="I14" t="n">
-        <v>153.2</v>
+        <v>126.9</v>
       </c>
       <c r="J14" t="n">
-        <v>9.17</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>2.379</v>
+        <v>1.605</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1227,28 +1227,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.4</v>
+        <v>66.3</v>
       </c>
       <c r="E15" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="F15" t="n">
-        <v>1.608</v>
+        <v>6.564</v>
       </c>
       <c r="G15" t="n">
-        <v>4.031</v>
+        <v>14.821</v>
       </c>
       <c r="H15" t="n">
-        <v>4.07</v>
+        <v>4.47</v>
       </c>
       <c r="I15" t="n">
-        <v>150.7</v>
+        <v>125.8</v>
       </c>
       <c r="J15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="K15" t="n">
-        <v>1.605</v>
+        <v>2.379</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1281,28 +1281,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7.6</v>
+        <v>17.7</v>
       </c>
       <c r="E16" t="n">
-        <v>9.5</v>
+        <v>10.6</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8</v>
+        <v>1.67</v>
       </c>
       <c r="G16" t="n">
-        <v>1.957</v>
+        <v>3.588</v>
       </c>
       <c r="H16" t="n">
-        <v>3.88</v>
+        <v>4.93</v>
       </c>
       <c r="I16" t="n">
-        <v>144.7</v>
+        <v>114.9</v>
       </c>
       <c r="J16" t="n">
-        <v>10.53</v>
+        <v>9.43</v>
       </c>
       <c r="K16" t="n">
-        <v>1.794</v>
+        <v>1.677</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1331,40 +1331,40 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.39</v>
+        <v>37.14</v>
       </c>
       <c r="E17" t="n">
-        <v>13</v>
+        <v>4.6</v>
       </c>
       <c r="F17" t="n">
-        <v>0.03</v>
+        <v>8.074</v>
       </c>
       <c r="G17" t="n">
-        <v>0.073</v>
+        <v>15.876</v>
       </c>
       <c r="H17" t="n">
-        <v>5.32</v>
+        <v>2.34</v>
       </c>
       <c r="I17" t="n">
-        <v>144.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>7.69</v>
+        <v>21.74</v>
       </c>
       <c r="K17" t="n">
-        <v>1.167</v>
+        <v>1.669</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>mid-cycle</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1389,25 +1389,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>77.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="E18" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>8.663</v>
+        <v>10.023</v>
       </c>
       <c r="G18" t="n">
         <v>18.535</v>
       </c>
       <c r="H18" t="n">
-        <v>4.16</v>
+        <v>4.76</v>
       </c>
       <c r="I18" t="n">
-        <v>114</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>11.24</v>
+        <v>11.36</v>
       </c>
       <c r="K18" t="n">
         <v>1.781</v>
@@ -1429,7 +1429,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1439,32 +1439,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>37.14</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>4.6</v>
+        <v>14</v>
       </c>
       <c r="F19" t="n">
-        <v>8.074</v>
+        <v>5.529</v>
       </c>
       <c r="G19" t="n">
-        <v>15.876</v>
+        <v>9.677</v>
       </c>
       <c r="H19" t="n">
-        <v>2.34</v>
+        <v>8</v>
       </c>
       <c r="I19" t="n">
-        <v>96.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="J19" t="n">
-        <v>21.74</v>
+        <v>7.14</v>
       </c>
       <c r="K19" t="n">
-        <v>1.669</v>
+        <v>1.807</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1497,25 +1497,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>31.3</v>
       </c>
       <c r="E20" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="F20" t="n">
-        <v>2.081</v>
+        <v>2.144</v>
       </c>
       <c r="G20" t="n">
         <v>3.74</v>
       </c>
       <c r="H20" t="n">
-        <v>8.289999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>79.8</v>
+        <v>74.5</v>
       </c>
       <c r="J20" t="n">
-        <v>6.71</v>
+        <v>6.85</v>
       </c>
       <c r="K20" t="n">
         <v>0.706</v>
@@ -1537,7 +1537,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BWLP</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1547,32 +1547,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>lpg</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>21.77</v>
+        <v>8.52</v>
       </c>
       <c r="E21" t="n">
-        <v>11.6</v>
+        <v>6.5</v>
       </c>
       <c r="F21" t="n">
-        <v>1.877</v>
+        <v>1.311</v>
       </c>
       <c r="G21" t="n">
-        <v>3.229</v>
+        <v>2.079</v>
       </c>
       <c r="H21" t="n">
-        <v>6.74</v>
+        <v>4.1</v>
       </c>
       <c r="I21" t="n">
-        <v>72</v>
+        <v>58.6</v>
       </c>
       <c r="J21" t="n">
-        <v>8.619999999999999</v>
+        <v>15.38</v>
       </c>
       <c r="K21" t="n">
-        <v>1.59</v>
+        <v>1.508</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>BWLP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1601,40 +1601,40 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>containerships</t>
+          <t>lpg</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.55</v>
+        <v>24.18</v>
       </c>
       <c r="E22" t="n">
-        <v>8.1</v>
+        <v>11.8</v>
       </c>
       <c r="F22" t="n">
-        <v>0.315</v>
+        <v>2.049</v>
       </c>
       <c r="G22" t="n">
-        <v>0.541</v>
+        <v>3.229</v>
       </c>
       <c r="H22" t="n">
-        <v>4.71</v>
+        <v>7.49</v>
       </c>
       <c r="I22" t="n">
-        <v>71.90000000000001</v>
+        <v>57.6</v>
       </c>
       <c r="J22" t="n">
-        <v>12.35</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>1.317</v>
+        <v>1.59</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1655,40 +1655,40 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>containerships</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>76.40000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="E23" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="F23" t="n">
-        <v>5.877</v>
+        <v>0.345</v>
       </c>
       <c r="G23" t="n">
-        <v>9.677</v>
+        <v>0.541</v>
       </c>
       <c r="H23" t="n">
-        <v>7.89</v>
+        <v>5.36</v>
       </c>
       <c r="I23" t="n">
-        <v>64.7</v>
+        <v>56.8</v>
       </c>
       <c r="J23" t="n">
-        <v>7.69</v>
+        <v>11.9</v>
       </c>
       <c r="K23" t="n">
-        <v>1.807</v>
+        <v>1.317</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1713,25 +1713,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28.6</v>
+        <v>30.4</v>
       </c>
       <c r="E24" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="F24" t="n">
-        <v>3.972</v>
+        <v>4.282</v>
       </c>
       <c r="G24" t="n">
         <v>5.97</v>
       </c>
       <c r="H24" t="n">
-        <v>4.79</v>
+        <v>5.09</v>
       </c>
       <c r="I24" t="n">
-        <v>50.3</v>
+        <v>39.4</v>
       </c>
       <c r="J24" t="n">
-        <v>13.89</v>
+        <v>14.08</v>
       </c>
       <c r="K24" t="n">
         <v>1.351</v>
@@ -1821,25 +1821,25 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>44.4</v>
+        <v>49.3</v>
       </c>
       <c r="E26" t="n">
-        <v>12.2</v>
+        <v>12.9</v>
       </c>
       <c r="F26" t="n">
-        <v>3.639</v>
+        <v>3.822</v>
       </c>
       <c r="G26" t="n">
         <v>4.357</v>
       </c>
       <c r="H26" t="n">
-        <v>10.19</v>
+        <v>11.31</v>
       </c>
       <c r="I26" t="n">
-        <v>19.7</v>
+        <v>14</v>
       </c>
       <c r="J26" t="n">
-        <v>8.199999999999999</v>
+        <v>7.75</v>
       </c>
       <c r="K26" t="n">
         <v>1.59</v>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -673,50 +673,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid proxy)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>99.3</v>
+        <v>17.25</v>
       </c>
       <c r="E5" t="n">
-        <v>13.9</v>
+        <v>10.5</v>
       </c>
       <c r="F5" t="n">
-        <v>7.144</v>
+        <v>1.643</v>
       </c>
       <c r="G5" t="n">
-        <v>20.633</v>
+        <v>4.899</v>
       </c>
       <c r="H5" t="n">
-        <v>4.81</v>
+        <v>3.52</v>
       </c>
       <c r="I5" t="n">
-        <v>188.8</v>
+        <v>198.2</v>
       </c>
       <c r="J5" t="n">
-        <v>7.19</v>
+        <v>9.52</v>
       </c>
       <c r="K5" t="n">
-        <v>2.101</v>
+        <v>1.412</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -727,42 +727,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid proxy)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31.8</v>
+        <v>99.3</v>
       </c>
       <c r="E6" t="n">
-        <v>10.6</v>
+        <v>13.9</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>7.144</v>
       </c>
       <c r="G6" t="n">
-        <v>8.631</v>
+        <v>20.633</v>
       </c>
       <c r="H6" t="n">
-        <v>3.68</v>
+        <v>4.81</v>
       </c>
       <c r="I6" t="n">
-        <v>187.7</v>
+        <v>188.8</v>
       </c>
       <c r="J6" t="n">
-        <v>9.43</v>
+        <v>7.19</v>
       </c>
       <c r="K6" t="n">
-        <v>1.844</v>
+        <v>2.101</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -791,40 +791,40 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>22.8</v>
+        <v>31.8</v>
       </c>
       <c r="E7" t="n">
-        <v>7.9</v>
+        <v>10.6</v>
       </c>
       <c r="F7" t="n">
-        <v>2.886</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>7.948</v>
+        <v>8.631</v>
       </c>
       <c r="H7" t="n">
-        <v>2.87</v>
+        <v>3.68</v>
       </c>
       <c r="I7" t="n">
-        <v>175.4</v>
+        <v>187.7</v>
       </c>
       <c r="J7" t="n">
-        <v>12.66</v>
+        <v>9.43</v>
       </c>
       <c r="K7" t="n">
-        <v>0.781</v>
+        <v>1.844</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>below-mid</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -845,40 +845,40 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>lng</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.25</v>
+        <v>22.8</v>
       </c>
       <c r="E8" t="n">
-        <v>10.5</v>
+        <v>7.9</v>
       </c>
       <c r="F8" t="n">
-        <v>1.643</v>
+        <v>2.886</v>
       </c>
       <c r="G8" t="n">
-        <v>4.362</v>
+        <v>7.948</v>
       </c>
       <c r="H8" t="n">
-        <v>3.96</v>
+        <v>2.87</v>
       </c>
       <c r="I8" t="n">
-        <v>165.5</v>
+        <v>175.4</v>
       </c>
       <c r="J8" t="n">
-        <v>9.52</v>
+        <v>12.66</v>
       </c>
       <c r="K8" t="n">
-        <v>1.306</v>
+        <v>0.781</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>below-mid</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -899,40 +899,40 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19.4</v>
+        <v>25.8</v>
       </c>
       <c r="E9" t="n">
-        <v>9.9</v>
+        <v>12.3</v>
       </c>
       <c r="F9" t="n">
-        <v>1.96</v>
+        <v>2.098</v>
       </c>
       <c r="G9" t="n">
-        <v>5.028</v>
+        <v>5.537</v>
       </c>
       <c r="H9" t="n">
-        <v>3.86</v>
+        <v>4.66</v>
       </c>
       <c r="I9" t="n">
-        <v>156.6</v>
+        <v>164</v>
       </c>
       <c r="J9" t="n">
-        <v>10.1</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>2.643</v>
+        <v>1.412</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -953,40 +953,40 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8.300000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="E10" t="n">
-        <v>10.4</v>
+        <v>17.8</v>
       </c>
       <c r="F10" t="n">
-        <v>0.798</v>
+        <v>0.03</v>
       </c>
       <c r="G10" t="n">
-        <v>1.957</v>
+        <v>0.079</v>
       </c>
       <c r="H10" t="n">
-        <v>4.24</v>
+        <v>6.75</v>
       </c>
       <c r="I10" t="n">
-        <v>145.3</v>
+        <v>163.8</v>
       </c>
       <c r="J10" t="n">
-        <v>9.619999999999999</v>
+        <v>5.62</v>
       </c>
       <c r="K10" t="n">
-        <v>1.794</v>
+        <v>1.202</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1007,40 +1007,40 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.53</v>
+        <v>19.4</v>
       </c>
       <c r="E11" t="n">
-        <v>17.8</v>
+        <v>9.9</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03</v>
+        <v>1.96</v>
       </c>
       <c r="G11" t="n">
-        <v>0.073</v>
+        <v>5.028</v>
       </c>
       <c r="H11" t="n">
-        <v>7.26</v>
+        <v>3.86</v>
       </c>
       <c r="I11" t="n">
-        <v>145.2</v>
+        <v>156.6</v>
       </c>
       <c r="J11" t="n">
-        <v>5.62</v>
+        <v>10.1</v>
       </c>
       <c r="K11" t="n">
-        <v>1.167</v>
+        <v>2.643</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>mid-cycle</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1061,32 +1061,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>43.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="F12" t="n">
-        <v>4.252</v>
+        <v>0.798</v>
       </c>
       <c r="G12" t="n">
-        <v>10.235</v>
+        <v>1.957</v>
       </c>
       <c r="H12" t="n">
-        <v>4.28</v>
+        <v>4.24</v>
       </c>
       <c r="I12" t="n">
-        <v>140.7</v>
+        <v>145.3</v>
       </c>
       <c r="J12" t="n">
-        <v>9.710000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>2.43</v>
+        <v>1.794</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1115,40 +1115,40 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>25.8</v>
+        <v>18.3</v>
       </c>
       <c r="E13" t="n">
-        <v>12.3</v>
+        <v>10.3</v>
       </c>
       <c r="F13" t="n">
-        <v>2.098</v>
+        <v>1.777</v>
       </c>
       <c r="G13" t="n">
-        <v>4.989</v>
+        <v>4.348</v>
       </c>
       <c r="H13" t="n">
-        <v>5.17</v>
+        <v>4.21</v>
       </c>
       <c r="I13" t="n">
-        <v>137.9</v>
+        <v>144.7</v>
       </c>
       <c r="J13" t="n">
-        <v>8.130000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>1.284</v>
+        <v>1.715</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1173,28 +1173,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.3</v>
+        <v>43.8</v>
       </c>
       <c r="E14" t="n">
         <v>10.3</v>
       </c>
       <c r="F14" t="n">
-        <v>1.777</v>
+        <v>4.252</v>
       </c>
       <c r="G14" t="n">
-        <v>4.031</v>
+        <v>10.235</v>
       </c>
       <c r="H14" t="n">
-        <v>4.54</v>
+        <v>4.28</v>
       </c>
       <c r="I14" t="n">
-        <v>126.9</v>
+        <v>140.7</v>
       </c>
       <c r="J14" t="n">
         <v>9.710000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>1.605</v>
+        <v>2.43</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1560,19 +1560,19 @@
         <v>1.311</v>
       </c>
       <c r="G21" t="n">
-        <v>2.079</v>
+        <v>2.135</v>
       </c>
       <c r="H21" t="n">
-        <v>4.1</v>
+        <v>3.99</v>
       </c>
       <c r="I21" t="n">
-        <v>58.6</v>
+        <v>62.9</v>
       </c>
       <c r="J21" t="n">
         <v>15.38</v>
       </c>
       <c r="K21" t="n">
-        <v>1.508</v>
+        <v>1.624</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1722,19 +1722,19 @@
         <v>4.282</v>
       </c>
       <c r="G24" t="n">
-        <v>5.97</v>
+        <v>6.555</v>
       </c>
       <c r="H24" t="n">
-        <v>5.09</v>
+        <v>4.64</v>
       </c>
       <c r="I24" t="n">
-        <v>39.4</v>
+        <v>53.1</v>
       </c>
       <c r="J24" t="n">
         <v>14.08</v>
       </c>
       <c r="K24" t="n">
-        <v>1.351</v>
+        <v>1.466</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1591,7 +1591,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BWLP</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1601,40 +1601,40 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>lpg</t>
+          <t>containerships</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>24.18</v>
+        <v>2.9</v>
       </c>
       <c r="E22" t="n">
-        <v>11.8</v>
+        <v>8.4</v>
       </c>
       <c r="F22" t="n">
-        <v>2.049</v>
+        <v>0.345</v>
       </c>
       <c r="G22" t="n">
-        <v>3.229</v>
+        <v>0.549</v>
       </c>
       <c r="H22" t="n">
-        <v>7.49</v>
+        <v>5.28</v>
       </c>
       <c r="I22" t="n">
-        <v>57.6</v>
+        <v>59</v>
       </c>
       <c r="J22" t="n">
-        <v>8.470000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="K22" t="n">
-        <v>1.59</v>
+        <v>1.319</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>BWLP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1655,40 +1655,40 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>containerships</t>
+          <t>lpg</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2.9</v>
+        <v>24.18</v>
       </c>
       <c r="E23" t="n">
-        <v>8.4</v>
+        <v>11.8</v>
       </c>
       <c r="F23" t="n">
-        <v>0.345</v>
+        <v>2.049</v>
       </c>
       <c r="G23" t="n">
-        <v>0.541</v>
+        <v>3.229</v>
       </c>
       <c r="H23" t="n">
-        <v>5.36</v>
+        <v>7.49</v>
       </c>
       <c r="I23" t="n">
-        <v>56.8</v>
+        <v>57.6</v>
       </c>
       <c r="J23" t="n">
-        <v>11.9</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>1.317</v>
+        <v>1.59</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -1051,7 +1051,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1061,32 +1061,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8.300000000000001</v>
+        <v>18.3</v>
       </c>
       <c r="E12" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="F12" t="n">
-        <v>0.798</v>
+        <v>1.777</v>
       </c>
       <c r="G12" t="n">
-        <v>1.957</v>
+        <v>4.348</v>
       </c>
       <c r="H12" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="I12" t="n">
-        <v>145.3</v>
+        <v>144.7</v>
       </c>
       <c r="J12" t="n">
-        <v>9.619999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>1.794</v>
+        <v>1.715</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1119,28 +1119,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.3</v>
+        <v>43.8</v>
       </c>
       <c r="E13" t="n">
         <v>10.3</v>
       </c>
       <c r="F13" t="n">
-        <v>1.777</v>
+        <v>4.252</v>
       </c>
       <c r="G13" t="n">
-        <v>4.348</v>
+        <v>9.9</v>
       </c>
       <c r="H13" t="n">
-        <v>4.21</v>
+        <v>4.42</v>
       </c>
       <c r="I13" t="n">
-        <v>144.7</v>
+        <v>132.8</v>
       </c>
       <c r="J13" t="n">
         <v>9.710000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>1.715</v>
+        <v>2.434</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1173,28 +1173,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>43.8</v>
+        <v>66.3</v>
       </c>
       <c r="E14" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="F14" t="n">
-        <v>4.252</v>
+        <v>6.564</v>
       </c>
       <c r="G14" t="n">
-        <v>10.235</v>
+        <v>14.821</v>
       </c>
       <c r="H14" t="n">
-        <v>4.28</v>
+        <v>4.47</v>
       </c>
       <c r="I14" t="n">
-        <v>140.7</v>
+        <v>125.8</v>
       </c>
       <c r="J14" t="n">
-        <v>9.710000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="K14" t="n">
-        <v>2.43</v>
+        <v>2.379</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1223,32 +1223,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>66.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="F15" t="n">
-        <v>6.564</v>
+        <v>0.798</v>
       </c>
       <c r="G15" t="n">
-        <v>14.821</v>
+        <v>1.756</v>
       </c>
       <c r="H15" t="n">
-        <v>4.47</v>
+        <v>4.73</v>
       </c>
       <c r="I15" t="n">
-        <v>125.8</v>
+        <v>120.1</v>
       </c>
       <c r="J15" t="n">
-        <v>9.9</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>2.379</v>
+        <v>1.801</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -534,19 +534,19 @@
         <v>0.63</v>
       </c>
       <c r="G2" t="n">
-        <v>2.905</v>
+        <v>2.583</v>
       </c>
       <c r="H2" t="n">
-        <v>5.53</v>
+        <v>6.22</v>
       </c>
       <c r="I2" t="n">
-        <v>361.3</v>
+        <v>310.2</v>
       </c>
       <c r="J2" t="n">
         <v>3.92</v>
       </c>
       <c r="K2" t="n">
-        <v>2.316</v>
+        <v>2.356</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>

--- a/outputs/consensus_eps_xref.xlsx
+++ b/outputs/consensus_eps_xref.xlsx
@@ -696,19 +696,19 @@
         <v>1.643</v>
       </c>
       <c r="G5" t="n">
-        <v>4.899</v>
+        <v>5.305</v>
       </c>
       <c r="H5" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="I5" t="n">
-        <v>198.2</v>
+        <v>222.9</v>
       </c>
       <c r="J5" t="n">
         <v>9.52</v>
       </c>
       <c r="K5" t="n">
-        <v>1.412</v>
+        <v>1.479</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -845,40 +845,40 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>22.8</v>
+        <v>25.8</v>
       </c>
       <c r="E8" t="n">
-        <v>7.9</v>
+        <v>12.3</v>
       </c>
       <c r="F8" t="n">
-        <v>2.886</v>
+        <v>2.098</v>
       </c>
       <c r="G8" t="n">
-        <v>7.948</v>
+        <v>5.909</v>
       </c>
       <c r="H8" t="n">
-        <v>2.87</v>
+        <v>4.37</v>
       </c>
       <c r="I8" t="n">
-        <v>175.4</v>
+        <v>181.7</v>
       </c>
       <c r="J8" t="n">
-        <v>12.66</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.781</v>
+        <v>1.482</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>below-mid</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -903,28 +903,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>25.8</v>
+        <v>0.53</v>
       </c>
       <c r="E9" t="n">
-        <v>12.3</v>
+        <v>17.8</v>
       </c>
       <c r="F9" t="n">
-        <v>2.098</v>
+        <v>0.03</v>
       </c>
       <c r="G9" t="n">
-        <v>5.537</v>
+        <v>0.083</v>
       </c>
       <c r="H9" t="n">
-        <v>4.66</v>
+        <v>6.4</v>
       </c>
       <c r="I9" t="n">
-        <v>164</v>
+        <v>178.2</v>
       </c>
       <c r="J9" t="n">
-        <v>8.130000000000001</v>
+        <v>5.62</v>
       </c>
       <c r="K9" t="n">
-        <v>1.412</v>
+        <v>1.23</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -953,40 +953,40 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>lng</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.53</v>
+        <v>22.8</v>
       </c>
       <c r="E10" t="n">
-        <v>17.8</v>
+        <v>7.9</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03</v>
+        <v>2.886</v>
       </c>
       <c r="G10" t="n">
-        <v>0.079</v>
+        <v>7.948</v>
       </c>
       <c r="H10" t="n">
-        <v>6.75</v>
+        <v>2.87</v>
       </c>
       <c r="I10" t="n">
-        <v>163.8</v>
+        <v>175.4</v>
       </c>
       <c r="J10" t="n">
-        <v>5.62</v>
+        <v>12.66</v>
       </c>
       <c r="K10" t="n">
-        <v>1.202</v>
+        <v>0.781</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>below-mid</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1011,28 +1011,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>19.4</v>
+        <v>18.3</v>
       </c>
       <c r="E11" t="n">
-        <v>9.9</v>
+        <v>10.3</v>
       </c>
       <c r="F11" t="n">
-        <v>1.96</v>
+        <v>1.777</v>
       </c>
       <c r="G11" t="n">
-        <v>5.028</v>
+        <v>4.57</v>
       </c>
       <c r="H11" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>156.6</v>
+        <v>157.2</v>
       </c>
       <c r="J11" t="n">
-        <v>10.1</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>2.643</v>
+        <v>1.772</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1065,28 +1065,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.3</v>
+        <v>19.4</v>
       </c>
       <c r="E12" t="n">
-        <v>10.3</v>
+        <v>9.9</v>
       </c>
       <c r="F12" t="n">
-        <v>1.777</v>
+        <v>1.96</v>
       </c>
       <c r="G12" t="n">
-        <v>4.348</v>
+        <v>5.028</v>
       </c>
       <c r="H12" t="n">
-        <v>4.21</v>
+        <v>3.86</v>
       </c>
       <c r="I12" t="n">
-        <v>144.7</v>
+        <v>156.6</v>
       </c>
       <c r="J12" t="n">
-        <v>9.710000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="K12" t="n">
-        <v>1.715</v>
+        <v>2.643</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1560,19 +1560,19 @@
         <v>1.311</v>
       </c>
       <c r="G21" t="n">
-        <v>2.135</v>
+        <v>2.191</v>
       </c>
       <c r="H21" t="n">
-        <v>3.99</v>
+        <v>3.89</v>
       </c>
       <c r="I21" t="n">
-        <v>62.9</v>
+        <v>67.2</v>
       </c>
       <c r="J21" t="n">
         <v>15.38</v>
       </c>
       <c r="K21" t="n">
-        <v>1.624</v>
+        <v>1.705</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1601,40 +1601,40 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>containerships</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.9</v>
+        <v>30.4</v>
       </c>
       <c r="E22" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
       <c r="F22" t="n">
-        <v>0.345</v>
+        <v>4.282</v>
       </c>
       <c r="G22" t="n">
-        <v>0.549</v>
+        <v>7.005</v>
       </c>
       <c r="H22" t="n">
-        <v>5.28</v>
+        <v>4.34</v>
       </c>
       <c r="I22" t="n">
-        <v>59</v>
+        <v>63.6</v>
       </c>
       <c r="J22" t="n">
-        <v>11.9</v>
+        <v>14.08</v>
       </c>
       <c r="K22" t="n">
-        <v>1.319</v>
+        <v>1.537</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BWLP</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1655,40 +1655,40 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>lpg</t>
+          <t>containerships</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>24.18</v>
+        <v>2.9</v>
       </c>
       <c r="E23" t="n">
-        <v>11.8</v>
+        <v>8.4</v>
       </c>
       <c r="F23" t="n">
-        <v>2.049</v>
+        <v>0.345</v>
       </c>
       <c r="G23" t="n">
-        <v>3.229</v>
+        <v>0.549</v>
       </c>
       <c r="H23" t="n">
-        <v>7.49</v>
+        <v>5.28</v>
       </c>
       <c r="I23" t="n">
-        <v>57.6</v>
+        <v>59</v>
       </c>
       <c r="J23" t="n">
-        <v>8.470000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="K23" t="n">
-        <v>1.59</v>
+        <v>1.319</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>BWLP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1709,40 +1709,40 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>lpg</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>30.4</v>
+        <v>24.18</v>
       </c>
       <c r="E24" t="n">
-        <v>7.1</v>
+        <v>11.8</v>
       </c>
       <c r="F24" t="n">
-        <v>4.282</v>
+        <v>2.049</v>
       </c>
       <c r="G24" t="n">
-        <v>6.555</v>
+        <v>3.229</v>
       </c>
       <c r="H24" t="n">
-        <v>4.64</v>
+        <v>7.49</v>
       </c>
       <c r="I24" t="n">
-        <v>53.1</v>
+        <v>57.6</v>
       </c>
       <c r="J24" t="n">
-        <v>14.08</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>1.466</v>
+        <v>1.59</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
